--- a/data/raw/gee_genie_electrique.xlsx
+++ b/data/raw/gee_genie_electrique.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1ère Année" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2ème Année" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3ème Année" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -63,17 +64,44 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="00006100"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="00AAAAAA"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00006100"/>
+      <color rgb="007030A0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00888888"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="007030A0"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="29">
     <fill>
       <patternFill/>
     </fill>
@@ -82,12 +110,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001B3A2E"/>
+        <fgColor rgb="001B3A4A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00276749"/>
+        <fgColor rgb="002B6CB0"/>
       </patternFill>
     </fill>
     <fill>
@@ -122,12 +150,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAD3"/>
+        <fgColor rgb="00D6EAF8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EAF4EA"/>
+        <fgColor rgb="00E8F8F5"/>
       </patternFill>
     </fill>
     <fill>
@@ -157,11 +185,66 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2FAF4"/>
+        <fgColor rgb="00F0F7FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001B3A2D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E7D52"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D5E8D4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDE1F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FFFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007030A0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF9E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FFFD"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -183,11 +266,55 @@
         <color rgb="00AAAAAA"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00AAAAAA"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00AAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00AAAAAA"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00AAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00AAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00AAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00AAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00AAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -234,23 +361,73 @@
     <xf numFmtId="0" fontId="6" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -621,8 +798,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
@@ -654,6 +831,31 @@
           <t>DÉPARTEMENT GEE — GÉNIE ÉLECTRIQUE ET ÉLECTRONIQUE — PREMIÈRE ANNÉE</t>
         </is>
       </c>
+      <c r="B1" s="22" t="n"/>
+      <c r="C1" s="22" t="n"/>
+      <c r="D1" s="22" t="n"/>
+      <c r="E1" s="22" t="n"/>
+      <c r="F1" s="22" t="n"/>
+      <c r="G1" s="22" t="n"/>
+      <c r="H1" s="22" t="n"/>
+      <c r="I1" s="22" t="n"/>
+      <c r="J1" s="22" t="n"/>
+      <c r="K1" s="22" t="n"/>
+      <c r="L1" s="22" t="n"/>
+      <c r="M1" s="22" t="n"/>
+      <c r="N1" s="22" t="n"/>
+      <c r="O1" s="22" t="n"/>
+      <c r="P1" s="22" t="n"/>
+      <c r="Q1" s="22" t="n"/>
+      <c r="R1" s="22" t="n"/>
+      <c r="S1" s="22" t="n"/>
+      <c r="T1" s="22" t="n"/>
+      <c r="U1" s="22" t="n"/>
+      <c r="V1" s="22" t="n"/>
+      <c r="W1" s="22" t="n"/>
+      <c r="X1" s="22" t="n"/>
+      <c r="Y1" s="22" t="n"/>
+      <c r="Z1" s="23" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -661,22 +863,44 @@
           <t>Informations Générales</t>
         </is>
       </c>
+      <c r="B2" s="22" t="n"/>
+      <c r="C2" s="23" t="n"/>
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>SEMESTRE 1</t>
         </is>
       </c>
+      <c r="E2" s="22" t="n"/>
+      <c r="F2" s="22" t="n"/>
+      <c r="G2" s="22" t="n"/>
+      <c r="H2" s="22" t="n"/>
+      <c r="I2" s="22" t="n"/>
+      <c r="J2" s="22" t="n"/>
+      <c r="K2" s="22" t="n"/>
+      <c r="L2" s="22" t="n"/>
+      <c r="M2" s="23" t="n"/>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>SEMESTRE 2</t>
         </is>
       </c>
+      <c r="O2" s="22" t="n"/>
+      <c r="P2" s="22" t="n"/>
+      <c r="Q2" s="22" t="n"/>
+      <c r="R2" s="22" t="n"/>
+      <c r="S2" s="22" t="n"/>
+      <c r="T2" s="22" t="n"/>
+      <c r="U2" s="22" t="n"/>
+      <c r="V2" s="22" t="n"/>
+      <c r="W2" s="23" t="n"/>
       <c r="X2" s="2" t="n"/>
       <c r="Y2" s="2" t="n"/>
       <c r="Z2" s="2" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="3" t="n"/>
+      <c r="B3" s="22" t="n"/>
+      <c r="C3" s="23" t="n"/>
       <c r="D3" s="4" t="n"/>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -803,7 +1027,7 @@
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>Systèmes Logiques</t>
+          <t>Systèmes Numériques</t>
         </is>
       </c>
       <c r="J4" s="6" t="inlineStr">
@@ -834,7 +1058,7 @@
       </c>
       <c r="P4" s="8" t="inlineStr">
         <is>
-          <t>Électronique Numérique</t>
+          <t>Électronique de Puissance</t>
         </is>
       </c>
       <c r="Q4" s="8" t="inlineStr">
@@ -844,12 +1068,12 @@
       </c>
       <c r="R4" s="8" t="inlineStr">
         <is>
+          <t>Automatique 1</t>
+        </is>
+      </c>
+      <c r="S4" s="8" t="inlineStr">
+        <is>
           <t>Électromagnétisme</t>
-        </is>
-      </c>
-      <c r="S4" s="8" t="inlineStr">
-        <is>
-          <t>Automatique 1</t>
         </is>
       </c>
       <c r="T4" s="8" t="inlineStr">
@@ -900,80 +1124,80 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Aarab</t>
+          <t>Akhchichane</t>
         </is>
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>Yassine</t>
+          <t>Youssef</t>
         </is>
       </c>
       <c r="D5" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>12.18</v>
-      </c>
-      <c r="F5" s="16" t="n">
-        <v>11.62</v>
+        <v>17.37</v>
+      </c>
+      <c r="F5" s="15" t="n">
+        <v>16.82</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>14.31</v>
+        <v>19.46</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>13.48</v>
-      </c>
-      <c r="I5" s="16" t="n">
-        <v>9.81</v>
-      </c>
-      <c r="J5" s="16" t="n">
-        <v>8.470000000000001</v>
-      </c>
-      <c r="K5" s="16" t="n">
-        <v>8.27</v>
-      </c>
-      <c r="M5" s="17" t="n">
-        <v>11.51</v>
+        <v>18.65</v>
+      </c>
+      <c r="I5" s="15" t="n">
+        <v>15.05</v>
+      </c>
+      <c r="J5" s="15" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="K5" s="15" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="M5" s="16" t="n">
+        <v>16.72</v>
       </c>
       <c r="N5" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="O5" s="16" t="n">
-        <v>11.97</v>
+      <c r="O5" s="15" t="n">
+        <v>17.17</v>
       </c>
       <c r="P5" s="15" t="n">
-        <v>13.4</v>
+        <v>18.57</v>
       </c>
       <c r="Q5" s="15" t="n">
-        <v>12.19</v>
+        <v>17.38</v>
       </c>
       <c r="R5" s="15" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="S5" s="16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="T5" s="16" t="n">
-        <v>6.96</v>
-      </c>
-      <c r="U5" s="16" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="V5" s="16" t="n">
-        <v>9.06</v>
-      </c>
-      <c r="W5" s="17" t="n">
-        <v>9.390000000000001</v>
+        <v>17.49</v>
+      </c>
+      <c r="S5" s="17" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="T5" s="15" t="n">
+        <v>12.26</v>
+      </c>
+      <c r="U5" s="17" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="V5" s="15" t="n">
+        <v>14.32</v>
+      </c>
+      <c r="W5" s="16" t="n">
+        <v>14.63</v>
       </c>
       <c r="X5" s="18" t="n">
-        <v>10.45</v>
+        <v>15.68</v>
       </c>
       <c r="Y5" s="11" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Z5" s="19" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non</t>
         </is>
       </c>
     </row>
@@ -985,78 +1209,78 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>Bahraoui</t>
+          <t>Benbrahim</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>Nora</t>
+          <t>Nadia</t>
         </is>
       </c>
       <c r="D6" s="14" t="n">
-        <v>17</v>
-      </c>
-      <c r="E6" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <v>17.72</v>
+      </c>
+      <c r="G6" s="17" t="n">
         <v>9.81</v>
       </c>
-      <c r="F6" s="15" t="n">
+      <c r="H6" s="15" t="n">
         <v>16.11</v>
       </c>
-      <c r="G6" s="15" t="n">
+      <c r="I6" s="15" t="n">
         <v>14.33</v>
       </c>
-      <c r="H6" s="16" t="n">
+      <c r="J6" s="17" t="n">
         <v>9.66</v>
       </c>
-      <c r="I6" s="15" t="n">
+      <c r="K6" s="15" t="n">
         <v>19.23</v>
       </c>
-      <c r="J6" s="15" t="n">
-        <v>13.96</v>
-      </c>
-      <c r="K6" s="15" t="n">
+      <c r="M6" s="16" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="N6" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="O6" s="15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="P6" s="15" t="n">
         <v>12.81</v>
       </c>
-      <c r="M6" s="17" t="n">
+      <c r="Q6" s="15" t="n">
         <v>13.69</v>
       </c>
-      <c r="N6" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="O6" s="15" t="n">
-        <v>13.69</v>
-      </c>
-      <c r="P6" s="15" t="n">
+      <c r="R6" s="15" t="n">
         <v>14.44</v>
       </c>
-      <c r="Q6" s="15" t="n">
+      <c r="S6" s="15" t="n">
         <v>19.28</v>
       </c>
-      <c r="R6" s="15" t="n">
+      <c r="T6" s="15" t="n">
         <v>13.89</v>
       </c>
-      <c r="S6" s="15" t="n">
+      <c r="U6" s="15" t="n">
         <v>18.08</v>
       </c>
-      <c r="T6" s="16" t="n">
+      <c r="V6" s="17" t="n">
         <v>10.68</v>
       </c>
-      <c r="U6" s="15" t="n">
-        <v>13.02</v>
-      </c>
-      <c r="V6" s="15" t="n">
-        <v>13.32</v>
-      </c>
-      <c r="W6" s="17" t="n">
-        <v>14.78</v>
+      <c r="W6" s="16" t="n">
+        <v>14.24</v>
       </c>
       <c r="X6" s="18" t="n">
-        <v>14.23</v>
+        <v>14.29</v>
       </c>
       <c r="Y6" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z6" s="21" t="inlineStr">
+      <c r="Z6" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -1070,7 +1294,7 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Chbihi</t>
+          <t>Chrif</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
@@ -1079,69 +1303,69 @@
         </is>
       </c>
       <c r="D7" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="E7" s="16" t="n">
-        <v>10.73</v>
+        <v>4</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>15</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>17.97</v>
+        <v>12.28</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>16.22</v>
-      </c>
-      <c r="H7" s="15" t="n">
-        <v>15.37</v>
-      </c>
-      <c r="I7" s="16" t="n">
-        <v>8.960000000000001</v>
+        <v>16.81</v>
+      </c>
+      <c r="H7" s="17" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="I7" s="15" t="n">
+        <v>12.8</v>
       </c>
       <c r="J7" s="15" t="n">
-        <v>12.27</v>
-      </c>
-      <c r="K7" s="15" t="n">
-        <v>13.96</v>
-      </c>
-      <c r="M7" s="17" t="n">
-        <v>13.81</v>
+        <v>18.98</v>
+      </c>
+      <c r="K7" s="17" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="M7" s="16" t="n">
+        <v>13.23</v>
       </c>
       <c r="N7" s="14" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="O7" s="15" t="n">
-        <v>13.34</v>
+        <v>15.25</v>
       </c>
       <c r="P7" s="15" t="n">
-        <v>16.42</v>
+        <v>15.47</v>
       </c>
       <c r="Q7" s="15" t="n">
-        <v>18.85</v>
+        <v>16.07</v>
       </c>
       <c r="R7" s="15" t="n">
-        <v>14.24</v>
+        <v>13.97</v>
       </c>
       <c r="S7" s="15" t="n">
-        <v>14.41</v>
+        <v>13.26</v>
       </c>
       <c r="T7" s="15" t="n">
-        <v>12.47</v>
-      </c>
-      <c r="U7" s="15" t="n">
-        <v>12.58</v>
-      </c>
-      <c r="V7" s="16" t="n">
-        <v>11.77</v>
-      </c>
-      <c r="W7" s="17" t="n">
-        <v>14.46</v>
+        <v>18.99</v>
+      </c>
+      <c r="U7" s="17" t="n">
+        <v>10.54</v>
+      </c>
+      <c r="V7" s="15" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="W7" s="16" t="n">
+        <v>15.01</v>
       </c>
       <c r="X7" s="18" t="n">
-        <v>14.14</v>
+        <v>14.12</v>
       </c>
       <c r="Y7" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z7" s="21" t="inlineStr">
+      <c r="Z7" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -1155,7 +1379,7 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Daoui</t>
+          <t>Dahak</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -1164,69 +1388,69 @@
         </is>
       </c>
       <c r="D8" s="14" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E8" s="15" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>13.29</v>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>16.69</v>
+      </c>
+      <c r="H8" s="17" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="I8" s="15" t="n">
         <v>16.78</v>
       </c>
-      <c r="F8" s="15" t="n">
+      <c r="J8" s="15" t="n">
         <v>19.34</v>
       </c>
-      <c r="G8" s="15" t="n">
+      <c r="K8" s="15" t="n">
         <v>16.71</v>
       </c>
-      <c r="H8" s="15" t="n">
+      <c r="M8" s="16" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="N8" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="O8" s="15" t="n">
         <v>12.04</v>
       </c>
-      <c r="I8" s="15" t="n">
+      <c r="P8" s="15" t="n">
         <v>17.71</v>
       </c>
-      <c r="J8" s="16" t="n">
+      <c r="Q8" s="17" t="n">
         <v>11.82</v>
       </c>
-      <c r="K8" s="16" t="n">
+      <c r="R8" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="M8" s="17" t="n">
+      <c r="S8" s="15" t="n">
+        <v>14.14</v>
+      </c>
+      <c r="T8" s="15" t="n">
+        <v>15.17</v>
+      </c>
+      <c r="U8" s="15" t="n">
         <v>15.57</v>
       </c>
-      <c r="N8" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="O8" s="15" t="n">
-        <v>14.14</v>
-      </c>
-      <c r="P8" s="15" t="n">
-        <v>15.17</v>
-      </c>
-      <c r="Q8" s="15" t="n">
-        <v>15.57</v>
-      </c>
-      <c r="R8" s="15" t="n">
+      <c r="V8" s="15" t="n">
         <v>13.91</v>
       </c>
-      <c r="S8" s="15" t="n">
-        <v>12.11</v>
-      </c>
-      <c r="T8" s="15" t="n">
-        <v>16.28</v>
-      </c>
-      <c r="U8" s="16" t="n">
-        <v>11.06</v>
-      </c>
-      <c r="V8" s="15" t="n">
-        <v>14.58</v>
-      </c>
-      <c r="W8" s="17" t="n">
-        <v>14.22</v>
+      <c r="W8" s="16" t="n">
+        <v>13.83</v>
       </c>
       <c r="X8" s="18" t="n">
-        <v>14.89</v>
+        <v>14.37</v>
       </c>
       <c r="Y8" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z8" s="21" t="inlineStr">
+      <c r="Z8" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -1240,7 +1464,7 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>El Aouni</t>
+          <t>El Boukili</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
@@ -1249,69 +1473,69 @@
         </is>
       </c>
       <c r="D9" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>12.98</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>13.84</v>
+      </c>
+      <c r="G9" s="15" t="n">
+        <v>18.76</v>
+      </c>
+      <c r="H9" s="17" t="n">
         <v>11.9</v>
       </c>
-      <c r="F9" s="15" t="n">
+      <c r="I9" s="15" t="n">
         <v>18.84</v>
       </c>
-      <c r="G9" s="15" t="n">
+      <c r="J9" s="15" t="n">
         <v>17.1</v>
       </c>
-      <c r="H9" s="15" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="I9" s="16" t="n">
+      <c r="K9" s="15" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="M9" s="16" t="n">
+        <v>15.34</v>
+      </c>
+      <c r="N9" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="O9" s="17" t="n">
         <v>11.89</v>
       </c>
-      <c r="J9" s="15" t="n">
+      <c r="P9" s="15" t="n">
         <v>14.01</v>
       </c>
-      <c r="K9" s="15" t="n">
+      <c r="Q9" s="15" t="n">
         <v>17.3</v>
       </c>
-      <c r="M9" s="17" t="n">
-        <v>15.02</v>
-      </c>
-      <c r="N9" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="O9" s="15" t="n">
+      <c r="R9" s="15" t="n">
         <v>13.62</v>
       </c>
-      <c r="P9" s="15" t="n">
+      <c r="S9" s="15" t="n">
+        <v>13.41</v>
+      </c>
+      <c r="T9" s="17" t="n">
+        <v>11.05</v>
+      </c>
+      <c r="U9" s="15" t="n">
+        <v>18.59</v>
+      </c>
+      <c r="V9" s="15" t="n">
         <v>14.65</v>
       </c>
-      <c r="Q9" s="16" t="n">
-        <v>11.05</v>
-      </c>
-      <c r="R9" s="15" t="n">
-        <v>18.59</v>
-      </c>
-      <c r="S9" s="15" t="n">
-        <v>13.11</v>
-      </c>
-      <c r="T9" s="15" t="n">
-        <v>12.65</v>
-      </c>
-      <c r="U9" s="15" t="n">
-        <v>14.49</v>
-      </c>
-      <c r="V9" s="15" t="n">
-        <v>16.11</v>
-      </c>
-      <c r="W9" s="17" t="n">
-        <v>14.28</v>
+      <c r="W9" s="16" t="n">
+        <v>14.3</v>
       </c>
       <c r="X9" s="18" t="n">
-        <v>14.65</v>
+        <v>14.82</v>
       </c>
       <c r="Y9" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z9" s="21" t="inlineStr">
+      <c r="Z9" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -1325,7 +1549,7 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Farissi</t>
+          <t>Fahr</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -1334,69 +1558,69 @@
         </is>
       </c>
       <c r="D10" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="E10" s="15" t="n">
-        <v>16.23</v>
+        <v>17</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>11.36</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>18.59</v>
+        <v>18.37</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>14.38</v>
-      </c>
-      <c r="H10" s="16" t="n">
-        <v>7.02</v>
+        <v>14.21</v>
+      </c>
+      <c r="H10" s="15" t="n">
+        <v>13.07</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>15.34</v>
+        <v>13.3</v>
       </c>
       <c r="J10" s="15" t="n">
-        <v>12.44</v>
-      </c>
-      <c r="K10" s="15" t="n">
-        <v>16.13</v>
-      </c>
-      <c r="M10" s="17" t="n">
-        <v>14.52</v>
+        <v>17.49</v>
+      </c>
+      <c r="K10" s="17" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="M10" s="16" t="n">
+        <v>14.06</v>
       </c>
       <c r="N10" s="14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O10" s="15" t="n">
-        <v>16.81</v>
-      </c>
-      <c r="P10" s="16" t="n">
-        <v>8.34</v>
+        <v>16.63</v>
+      </c>
+      <c r="P10" s="17" t="n">
+        <v>9.32</v>
       </c>
       <c r="Q10" s="15" t="n">
-        <v>14.1</v>
+        <v>17.05</v>
       </c>
       <c r="R10" s="15" t="n">
-        <v>15.04</v>
+        <v>18.27</v>
       </c>
       <c r="S10" s="15" t="n">
-        <v>18.58</v>
+        <v>18.03</v>
       </c>
       <c r="T10" s="15" t="n">
-        <v>14.67</v>
+        <v>18.73</v>
       </c>
       <c r="U10" s="15" t="n">
-        <v>14.69</v>
+        <v>16.06</v>
       </c>
       <c r="V10" s="15" t="n">
-        <v>16.61</v>
-      </c>
-      <c r="W10" s="17" t="n">
-        <v>14.76</v>
+        <v>13.64</v>
+      </c>
+      <c r="W10" s="16" t="n">
+        <v>15.67</v>
       </c>
       <c r="X10" s="18" t="n">
-        <v>14.64</v>
+        <v>14.87</v>
       </c>
       <c r="Y10" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z10" s="21" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="Z10" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -1410,7 +1634,7 @@
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>Grioui</t>
+          <t>Ghazali</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
@@ -1442,7 +1666,7 @@
       <c r="K11" s="15" t="n">
         <v>14.55</v>
       </c>
-      <c r="M11" s="17" t="n">
+      <c r="M11" s="16" t="n">
         <v>14.12</v>
       </c>
       <c r="N11" s="14" t="n">
@@ -1460,19 +1684,19 @@
       <c r="R11" s="15" t="n">
         <v>12.29</v>
       </c>
-      <c r="S11" s="16" t="n">
+      <c r="S11" s="17" t="n">
         <v>10.69</v>
       </c>
       <c r="T11" s="15" t="n">
         <v>12.68</v>
       </c>
-      <c r="U11" s="16" t="n">
+      <c r="U11" s="17" t="n">
         <v>9.43</v>
       </c>
-      <c r="V11" s="16" t="n">
+      <c r="V11" s="17" t="n">
         <v>8.82</v>
       </c>
-      <c r="W11" s="17" t="n">
+      <c r="W11" s="16" t="n">
         <v>11.64</v>
       </c>
       <c r="X11" s="18" t="n">
@@ -1481,7 +1705,7 @@
       <c r="Y11" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z11" s="21" t="inlineStr">
+      <c r="Z11" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -1495,7 +1719,7 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Hssaine</t>
+          <t>Hachimi</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -1506,7 +1730,7 @@
       <c r="D12" s="14" t="n">
         <v>14</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>9.81</v>
       </c>
       <c r="F12" s="15" t="n">
@@ -1515,7 +1739,7 @@
       <c r="G12" s="15" t="n">
         <v>17.49</v>
       </c>
-      <c r="H12" s="16" t="n">
+      <c r="H12" s="17" t="n">
         <v>9.880000000000001</v>
       </c>
       <c r="I12" s="15" t="n">
@@ -1527,7 +1751,7 @@
       <c r="K12" s="15" t="n">
         <v>13.81</v>
       </c>
-      <c r="M12" s="17" t="n">
+      <c r="M12" s="16" t="n">
         <v>13.91</v>
       </c>
       <c r="N12" s="14" t="n">
@@ -1536,7 +1760,7 @@
       <c r="O12" s="15" t="n">
         <v>12.15</v>
       </c>
-      <c r="P12" s="16" t="n">
+      <c r="P12" s="17" t="n">
         <v>11.79</v>
       </c>
       <c r="Q12" s="15" t="n">
@@ -1557,7 +1781,7 @@
       <c r="V12" s="15" t="n">
         <v>16.16</v>
       </c>
-      <c r="W12" s="17" t="n">
+      <c r="W12" s="16" t="n">
         <v>14.45</v>
       </c>
       <c r="X12" s="18" t="n">
@@ -1566,7 +1790,7 @@
       <c r="Y12" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z12" s="21" t="inlineStr">
+      <c r="Z12" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -1580,7 +1804,7 @@
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>Idhmad</t>
+          <t>Idali</t>
         </is>
       </c>
       <c r="C13" s="13" t="inlineStr">
@@ -1591,13 +1815,13 @@
       <c r="D13" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>11.13</v>
       </c>
       <c r="F13" s="15" t="n">
         <v>18.64</v>
       </c>
-      <c r="G13" s="16" t="n">
+      <c r="G13" s="17" t="n">
         <v>10.72</v>
       </c>
       <c r="H13" s="15" t="n">
@@ -1612,7 +1836,7 @@
       <c r="K13" s="15" t="n">
         <v>14.5</v>
       </c>
-      <c r="M13" s="17" t="n">
+      <c r="M13" s="16" t="n">
         <v>14.51</v>
       </c>
       <c r="N13" s="14" t="n">
@@ -1627,7 +1851,7 @@
       <c r="Q13" s="15" t="n">
         <v>16.12</v>
       </c>
-      <c r="R13" s="16" t="n">
+      <c r="R13" s="17" t="n">
         <v>11.07</v>
       </c>
       <c r="S13" s="15" t="n">
@@ -1642,7 +1866,7 @@
       <c r="V13" s="15" t="n">
         <v>16.24</v>
       </c>
-      <c r="W13" s="17" t="n">
+      <c r="W13" s="16" t="n">
         <v>14.61</v>
       </c>
       <c r="X13" s="18" t="n">
@@ -1651,7 +1875,7 @@
       <c r="Y13" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z13" s="21" t="inlineStr">
+      <c r="Z13" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -1665,7 +1889,7 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Jaouad</t>
+          <t>Jalili</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -1679,10 +1903,10 @@
       <c r="E14" s="15" t="n">
         <v>12.69</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="F14" s="17" t="n">
         <v>10.8</v>
       </c>
-      <c r="G14" s="16" t="n">
+      <c r="G14" s="17" t="n">
         <v>11.09</v>
       </c>
       <c r="H14" s="15" t="n">
@@ -1697,7 +1921,7 @@
       <c r="K14" s="15" t="n">
         <v>18.12</v>
       </c>
-      <c r="M14" s="17" t="n">
+      <c r="M14" s="16" t="n">
         <v>13.26</v>
       </c>
       <c r="N14" s="14" t="n">
@@ -1706,7 +1930,7 @@
       <c r="O14" s="15" t="n">
         <v>14.99</v>
       </c>
-      <c r="P14" s="16" t="n">
+      <c r="P14" s="17" t="n">
         <v>11.05</v>
       </c>
       <c r="Q14" s="15" t="n">
@@ -1727,7 +1951,7 @@
       <c r="V14" s="15" t="n">
         <v>13.96</v>
       </c>
-      <c r="W14" s="17" t="n">
+      <c r="W14" s="16" t="n">
         <v>15</v>
       </c>
       <c r="X14" s="18" t="n">
@@ -1736,7 +1960,7 @@
       <c r="Y14" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z14" s="21" t="inlineStr">
+      <c r="Z14" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -1750,7 +1974,7 @@
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>Kharbouch</t>
+          <t>Kaabi</t>
         </is>
       </c>
       <c r="C15" s="13" t="inlineStr">
@@ -1776,13 +2000,13 @@
       <c r="I15" s="15" t="n">
         <v>16.34</v>
       </c>
-      <c r="J15" s="16" t="n">
+      <c r="J15" s="17" t="n">
         <v>10.75</v>
       </c>
       <c r="K15" s="15" t="n">
         <v>14.65</v>
       </c>
-      <c r="M15" s="17" t="n">
+      <c r="M15" s="16" t="n">
         <v>14.92</v>
       </c>
       <c r="N15" s="14" t="n">
@@ -1797,7 +2021,7 @@
       <c r="Q15" s="15" t="n">
         <v>14.35</v>
       </c>
-      <c r="R15" s="16" t="n">
+      <c r="R15" s="17" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="S15" s="15" t="n">
@@ -1806,13 +2030,13 @@
       <c r="T15" s="15" t="n">
         <v>16.05</v>
       </c>
-      <c r="U15" s="16" t="n">
+      <c r="U15" s="17" t="n">
         <v>9.869999999999999</v>
       </c>
       <c r="V15" s="15" t="n">
         <v>16.6</v>
       </c>
-      <c r="W15" s="17" t="n">
+      <c r="W15" s="16" t="n">
         <v>14.17</v>
       </c>
       <c r="X15" s="18" t="n">
@@ -1821,7 +2045,7 @@
       <c r="Y15" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z15" s="21" t="inlineStr">
+      <c r="Z15" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -1835,7 +2059,7 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Laaziri</t>
+          <t>Lagrini</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -1852,7 +2076,7 @@
       <c r="F16" s="15" t="n">
         <v>13.36</v>
       </c>
-      <c r="G16" s="16" t="n">
+      <c r="G16" s="17" t="n">
         <v>9.880000000000001</v>
       </c>
       <c r="H16" s="15" t="n">
@@ -1867,19 +2091,19 @@
       <c r="K16" s="15" t="n">
         <v>12.67</v>
       </c>
-      <c r="M16" s="17" t="n">
+      <c r="M16" s="16" t="n">
         <v>13.75</v>
       </c>
       <c r="N16" s="14" t="n">
         <v>18</v>
       </c>
-      <c r="O16" s="16" t="n">
+      <c r="O16" s="17" t="n">
         <v>11.37</v>
       </c>
       <c r="P16" s="15" t="n">
         <v>18.75</v>
       </c>
-      <c r="Q16" s="16" t="n">
+      <c r="Q16" s="17" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="R16" s="15" t="n">
@@ -1897,7 +2121,7 @@
       <c r="V16" s="15" t="n">
         <v>15.45</v>
       </c>
-      <c r="W16" s="17" t="n">
+      <c r="W16" s="16" t="n">
         <v>15.56</v>
       </c>
       <c r="X16" s="18" t="n">
@@ -1906,7 +2130,7 @@
       <c r="Y16" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z16" s="21" t="inlineStr">
+      <c r="Z16" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -1920,7 +2144,7 @@
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>Maarouf</t>
+          <t>Mhammedi</t>
         </is>
       </c>
       <c r="C17" s="13" t="inlineStr">
@@ -1937,10 +2161,10 @@
       <c r="F17" s="15" t="n">
         <v>13.29</v>
       </c>
-      <c r="G17" s="16" t="n">
+      <c r="G17" s="17" t="n">
         <v>9.779999999999999</v>
       </c>
-      <c r="H17" s="16" t="n">
+      <c r="H17" s="17" t="n">
         <v>9.77</v>
       </c>
       <c r="I17" s="15" t="n">
@@ -1952,7 +2176,7 @@
       <c r="K17" s="15" t="n">
         <v>17.95</v>
       </c>
-      <c r="M17" s="17" t="n">
+      <c r="M17" s="16" t="n">
         <v>13.42</v>
       </c>
       <c r="N17" s="14" t="n">
@@ -1967,7 +2191,7 @@
       <c r="Q17" s="15" t="n">
         <v>12.9</v>
       </c>
-      <c r="R17" s="16" t="n">
+      <c r="R17" s="17" t="n">
         <v>10.1</v>
       </c>
       <c r="S17" s="15" t="n">
@@ -1982,7 +2206,7 @@
       <c r="V17" s="15" t="n">
         <v>17.53</v>
       </c>
-      <c r="W17" s="17" t="n">
+      <c r="W17" s="16" t="n">
         <v>14.02</v>
       </c>
       <c r="X17" s="18" t="n">
@@ -1991,7 +2215,7 @@
       <c r="Y17" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z17" s="21" t="inlineStr">
+      <c r="Z17" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -2005,7 +2229,7 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Nasri</t>
+          <t>Nassiri</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -2025,19 +2249,19 @@
       <c r="G18" s="15" t="n">
         <v>13.47</v>
       </c>
-      <c r="H18" s="16" t="n">
+      <c r="H18" s="17" t="n">
         <v>10.16</v>
       </c>
       <c r="I18" s="15" t="n">
         <v>14.83</v>
       </c>
-      <c r="J18" s="16" t="n">
+      <c r="J18" s="17" t="n">
         <v>10.72</v>
       </c>
       <c r="K18" s="15" t="n">
         <v>13.93</v>
       </c>
-      <c r="M18" s="17" t="n">
+      <c r="M18" s="16" t="n">
         <v>13.59</v>
       </c>
       <c r="N18" s="14" t="n">
@@ -2046,7 +2270,7 @@
       <c r="O18" s="15" t="n">
         <v>18.11</v>
       </c>
-      <c r="P18" s="16" t="n">
+      <c r="P18" s="17" t="n">
         <v>10.58</v>
       </c>
       <c r="Q18" s="15" t="n">
@@ -2067,7 +2291,7 @@
       <c r="V18" s="15" t="n">
         <v>15.18</v>
       </c>
-      <c r="W18" s="17" t="n">
+      <c r="W18" s="16" t="n">
         <v>15.22</v>
       </c>
       <c r="X18" s="18" t="n">
@@ -2076,7 +2300,7 @@
       <c r="Y18" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z18" s="21" t="inlineStr">
+      <c r="Z18" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -2090,7 +2314,7 @@
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>Ouhmad</t>
+          <t>Ouad</t>
         </is>
       </c>
       <c r="C19" s="13" t="inlineStr">
@@ -2101,13 +2325,13 @@
       <c r="D19" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="17" t="n">
         <v>11.67</v>
       </c>
       <c r="F19" s="15" t="n">
         <v>16.33</v>
       </c>
-      <c r="G19" s="16" t="n">
+      <c r="G19" s="17" t="n">
         <v>8.470000000000001</v>
       </c>
       <c r="H19" s="15" t="n">
@@ -2116,13 +2340,13 @@
       <c r="I19" s="15" t="n">
         <v>17.65</v>
       </c>
-      <c r="J19" s="16" t="n">
+      <c r="J19" s="17" t="n">
         <v>8.609999999999999</v>
       </c>
       <c r="K19" s="15" t="n">
         <v>12.11</v>
       </c>
-      <c r="M19" s="17" t="n">
+      <c r="M19" s="16" t="n">
         <v>13.53</v>
       </c>
       <c r="N19" s="14" t="n">
@@ -2152,7 +2376,7 @@
       <c r="V19" s="15" t="n">
         <v>15.43</v>
       </c>
-      <c r="W19" s="17" t="n">
+      <c r="W19" s="16" t="n">
         <v>15.5</v>
       </c>
       <c r="X19" s="18" t="n">
@@ -2161,7 +2385,7 @@
       <c r="Y19" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z19" s="21" t="inlineStr">
+      <c r="Z19" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -2175,7 +2399,7 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Qajjaj</t>
+          <t>Qaissi</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -2207,25 +2431,25 @@
       <c r="K20" s="15" t="n">
         <v>17.31</v>
       </c>
-      <c r="M20" s="17" t="n">
+      <c r="M20" s="16" t="n">
         <v>15.67</v>
       </c>
       <c r="N20" s="14" t="n">
         <v>14</v>
       </c>
-      <c r="O20" s="16" t="n">
+      <c r="O20" s="17" t="n">
         <v>10.75</v>
       </c>
       <c r="P20" s="15" t="n">
         <v>17.61</v>
       </c>
-      <c r="Q20" s="16" t="n">
+      <c r="Q20" s="17" t="n">
         <v>11.25</v>
       </c>
       <c r="R20" s="15" t="n">
         <v>15.92</v>
       </c>
-      <c r="S20" s="16" t="n">
+      <c r="S20" s="17" t="n">
         <v>9.880000000000001</v>
       </c>
       <c r="T20" s="15" t="n">
@@ -2237,7 +2461,7 @@
       <c r="V20" s="15" t="n">
         <v>12.38</v>
       </c>
-      <c r="W20" s="17" t="n">
+      <c r="W20" s="16" t="n">
         <v>13.3</v>
       </c>
       <c r="X20" s="18" t="n">
@@ -2246,7 +2470,7 @@
       <c r="Y20" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z20" s="21" t="inlineStr">
+      <c r="Z20" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -2260,7 +2484,7 @@
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>Rkibi</t>
+          <t>Regragui</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
@@ -2271,7 +2495,7 @@
       <c r="D21" s="14" t="n">
         <v>19</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="17" t="n">
         <v>10.86</v>
       </c>
       <c r="F21" s="15" t="n">
@@ -2286,13 +2510,13 @@
       <c r="I21" s="15" t="n">
         <v>13.02</v>
       </c>
-      <c r="J21" s="16" t="n">
+      <c r="J21" s="17" t="n">
         <v>11.65</v>
       </c>
       <c r="K21" s="15" t="n">
         <v>14.87</v>
       </c>
-      <c r="M21" s="17" t="n">
+      <c r="M21" s="16" t="n">
         <v>12.59</v>
       </c>
       <c r="N21" s="14" t="n">
@@ -2316,13 +2540,13 @@
       <c r="T21" s="15" t="n">
         <v>19.49</v>
       </c>
-      <c r="U21" s="16" t="n">
+      <c r="U21" s="17" t="n">
         <v>10.59</v>
       </c>
       <c r="V21" s="15" t="n">
         <v>13.4</v>
       </c>
-      <c r="W21" s="17" t="n">
+      <c r="W21" s="16" t="n">
         <v>14.58</v>
       </c>
       <c r="X21" s="18" t="n">
@@ -2331,7 +2555,7 @@
       <c r="Y21" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z21" s="21" t="inlineStr">
+      <c r="Z21" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -2345,7 +2569,7 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Sabri</t>
+          <t>Sekkat</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -2377,13 +2601,13 @@
       <c r="K22" s="15" t="n">
         <v>13.85</v>
       </c>
-      <c r="M22" s="17" t="n">
+      <c r="M22" s="16" t="n">
         <v>16.28</v>
       </c>
       <c r="N22" s="14" t="n">
         <v>14</v>
       </c>
-      <c r="O22" s="16" t="n">
+      <c r="O22" s="17" t="n">
         <v>9.880000000000001</v>
       </c>
       <c r="P22" s="15" t="n">
@@ -2392,7 +2616,7 @@
       <c r="Q22" s="15" t="n">
         <v>12.53</v>
       </c>
-      <c r="R22" s="16" t="n">
+      <c r="R22" s="17" t="n">
         <v>9.02</v>
       </c>
       <c r="S22" s="15" t="n">
@@ -2401,13 +2625,13 @@
       <c r="T22" s="15" t="n">
         <v>16.66</v>
       </c>
-      <c r="U22" s="16" t="n">
+      <c r="U22" s="17" t="n">
         <v>11.08</v>
       </c>
       <c r="V22" s="15" t="n">
         <v>12.39</v>
       </c>
-      <c r="W22" s="17" t="n">
+      <c r="W22" s="16" t="n">
         <v>12.04</v>
       </c>
       <c r="X22" s="18" t="n">
@@ -2416,7 +2640,7 @@
       <c r="Y22" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z22" s="21" t="inlineStr">
+      <c r="Z22" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -2430,7 +2654,7 @@
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>Toufiq</t>
+          <t>Tahri</t>
         </is>
       </c>
       <c r="C23" s="13" t="inlineStr">
@@ -2450,10 +2674,10 @@
       <c r="G23" s="15" t="n">
         <v>19.11</v>
       </c>
-      <c r="H23" s="16" t="n">
+      <c r="H23" s="17" t="n">
         <v>9.9</v>
       </c>
-      <c r="I23" s="16" t="n">
+      <c r="I23" s="17" t="n">
         <v>11.41</v>
       </c>
       <c r="J23" s="15" t="n">
@@ -2462,7 +2686,7 @@
       <c r="K23" s="15" t="n">
         <v>14.79</v>
       </c>
-      <c r="M23" s="17" t="n">
+      <c r="M23" s="16" t="n">
         <v>13.86</v>
       </c>
       <c r="N23" s="14" t="n">
@@ -2477,7 +2701,7 @@
       <c r="Q23" s="15" t="n">
         <v>14.86</v>
       </c>
-      <c r="R23" s="16" t="n">
+      <c r="R23" s="17" t="n">
         <v>11.91</v>
       </c>
       <c r="S23" s="15" t="n">
@@ -2492,7 +2716,7 @@
       <c r="V23" s="15" t="n">
         <v>17.11</v>
       </c>
-      <c r="W23" s="17" t="n">
+      <c r="W23" s="16" t="n">
         <v>15.93</v>
       </c>
       <c r="X23" s="18" t="n">
@@ -2501,7 +2725,7 @@
       <c r="Y23" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z23" s="21" t="inlineStr">
+      <c r="Z23" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -2515,7 +2739,7 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Uakkas</t>
+          <t>Ufkir</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -2532,10 +2756,10 @@
       <c r="F24" s="15" t="n">
         <v>16.65</v>
       </c>
-      <c r="G24" s="16" t="n">
+      <c r="G24" s="17" t="n">
         <v>11.43</v>
       </c>
-      <c r="H24" s="16" t="n">
+      <c r="H24" s="17" t="n">
         <v>9.93</v>
       </c>
       <c r="I24" s="15" t="n">
@@ -2544,10 +2768,10 @@
       <c r="J24" s="15" t="n">
         <v>13.79</v>
       </c>
-      <c r="K24" s="16" t="n">
+      <c r="K24" s="17" t="n">
         <v>11.64</v>
       </c>
-      <c r="M24" s="17" t="n">
+      <c r="M24" s="16" t="n">
         <v>13.08</v>
       </c>
       <c r="N24" s="14" t="n">
@@ -2577,7 +2801,7 @@
       <c r="V24" s="15" t="n">
         <v>13.09</v>
       </c>
-      <c r="W24" s="17" t="n">
+      <c r="W24" s="16" t="n">
         <v>14.94</v>
       </c>
       <c r="X24" s="18" t="n">
@@ -2586,7 +2810,7 @@
       <c r="Y24" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z24" s="21" t="inlineStr">
+      <c r="Z24" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -2600,7 +2824,7 @@
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>Venditti</t>
+          <t>Vantomme</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr">
@@ -2632,16 +2856,16 @@
       <c r="K25" s="15" t="n">
         <v>18.24</v>
       </c>
-      <c r="M25" s="17" t="n">
+      <c r="M25" s="16" t="n">
         <v>16.44</v>
       </c>
       <c r="N25" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="O25" s="16" t="n">
+      <c r="O25" s="17" t="n">
         <v>10.1</v>
       </c>
-      <c r="P25" s="16" t="n">
+      <c r="P25" s="17" t="n">
         <v>10.67</v>
       </c>
       <c r="Q25" s="15" t="n">
@@ -2650,7 +2874,7 @@
       <c r="R25" s="15" t="n">
         <v>15.15</v>
       </c>
-      <c r="S25" s="16" t="n">
+      <c r="S25" s="17" t="n">
         <v>10.65</v>
       </c>
       <c r="T25" s="15" t="n">
@@ -2662,7 +2886,7 @@
       <c r="V25" s="15" t="n">
         <v>14.82</v>
       </c>
-      <c r="W25" s="17" t="n">
+      <c r="W25" s="16" t="n">
         <v>13.87</v>
       </c>
       <c r="X25" s="18" t="n">
@@ -2671,7 +2895,7 @@
       <c r="Y25" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z25" s="21" t="inlineStr">
+      <c r="Z25" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -2685,7 +2909,7 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Wahnou</t>
+          <t>Wardi</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -2696,7 +2920,7 @@
       <c r="D26" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="E26" s="16" t="n">
+      <c r="E26" s="17" t="n">
         <v>10.37</v>
       </c>
       <c r="F26" s="15" t="n">
@@ -2717,7 +2941,7 @@
       <c r="K26" s="15" t="n">
         <v>14.48</v>
       </c>
-      <c r="M26" s="17" t="n">
+      <c r="M26" s="16" t="n">
         <v>14.85</v>
       </c>
       <c r="N26" s="14" t="n">
@@ -2738,16 +2962,16 @@
       <c r="S26" s="15" t="n">
         <v>12.23</v>
       </c>
-      <c r="T26" s="16" t="n">
+      <c r="T26" s="17" t="n">
         <v>9.039999999999999</v>
       </c>
       <c r="U26" s="15" t="n">
         <v>13.03</v>
       </c>
-      <c r="V26" s="16" t="n">
+      <c r="V26" s="17" t="n">
         <v>11.46</v>
       </c>
-      <c r="W26" s="17" t="n">
+      <c r="W26" s="16" t="n">
         <v>13.96</v>
       </c>
       <c r="X26" s="18" t="n">
@@ -2756,7 +2980,7 @@
       <c r="Y26" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z26" s="21" t="inlineStr">
+      <c r="Z26" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -2781,7 +3005,7 @@
       <c r="D27" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="E27" s="16" t="n">
+      <c r="E27" s="17" t="n">
         <v>11.7</v>
       </c>
       <c r="F27" s="15" t="n">
@@ -2802,7 +3026,7 @@
       <c r="K27" s="15" t="n">
         <v>14.01</v>
       </c>
-      <c r="M27" s="17" t="n">
+      <c r="M27" s="16" t="n">
         <v>15.6</v>
       </c>
       <c r="N27" s="14" t="n">
@@ -2820,19 +3044,19 @@
       <c r="R27" s="15" t="n">
         <v>17.31</v>
       </c>
-      <c r="S27" s="16" t="n">
+      <c r="S27" s="17" t="n">
         <v>11.24</v>
       </c>
       <c r="T27" s="15" t="n">
         <v>17.55</v>
       </c>
-      <c r="U27" s="16" t="n">
+      <c r="U27" s="17" t="n">
         <v>11.81</v>
       </c>
       <c r="V27" s="15" t="n">
         <v>14.61</v>
       </c>
-      <c r="W27" s="17" t="n">
+      <c r="W27" s="16" t="n">
         <v>14.26</v>
       </c>
       <c r="X27" s="18" t="n">
@@ -2841,7 +3065,7 @@
       <c r="Y27" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z27" s="21" t="inlineStr">
+      <c r="Z27" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -2855,7 +3079,7 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Yaakoubi</t>
+          <t>Yatribi</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -2872,7 +3096,7 @@
       <c r="F28" s="15" t="n">
         <v>12.66</v>
       </c>
-      <c r="G28" s="16" t="n">
+      <c r="G28" s="17" t="n">
         <v>11.71</v>
       </c>
       <c r="H28" s="15" t="n">
@@ -2881,13 +3105,13 @@
       <c r="I28" s="15" t="n">
         <v>14.52</v>
       </c>
-      <c r="J28" s="16" t="n">
+      <c r="J28" s="17" t="n">
         <v>10.69</v>
       </c>
       <c r="K28" s="15" t="n">
         <v>19.49</v>
       </c>
-      <c r="M28" s="17" t="n">
+      <c r="M28" s="16" t="n">
         <v>14.18</v>
       </c>
       <c r="N28" s="14" t="n">
@@ -2902,7 +3126,7 @@
       <c r="Q28" s="15" t="n">
         <v>14.52</v>
       </c>
-      <c r="R28" s="16" t="n">
+      <c r="R28" s="17" t="n">
         <v>9.539999999999999</v>
       </c>
       <c r="S28" s="15" t="n">
@@ -2917,7 +3141,7 @@
       <c r="V28" s="15" t="n">
         <v>12.16</v>
       </c>
-      <c r="W28" s="17" t="n">
+      <c r="W28" s="16" t="n">
         <v>14.57</v>
       </c>
       <c r="X28" s="18" t="n">
@@ -2926,7 +3150,7 @@
       <c r="Y28" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z28" s="21" t="inlineStr">
+      <c r="Z28" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -2940,7 +3164,7 @@
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>Zarhoun</t>
+          <t>Ziani</t>
         </is>
       </c>
       <c r="C29" s="13" t="inlineStr">
@@ -2966,19 +3190,19 @@
       <c r="I29" s="15" t="n">
         <v>14.24</v>
       </c>
-      <c r="J29" s="16" t="n">
+      <c r="J29" s="17" t="n">
         <v>10.96</v>
       </c>
       <c r="K29" s="15" t="n">
         <v>15.11</v>
       </c>
-      <c r="M29" s="17" t="n">
+      <c r="M29" s="16" t="n">
         <v>15.08</v>
       </c>
       <c r="N29" s="14" t="n">
         <v>18</v>
       </c>
-      <c r="O29" s="16" t="n">
+      <c r="O29" s="17" t="n">
         <v>11.96</v>
       </c>
       <c r="P29" s="15" t="n">
@@ -2999,10 +3223,10 @@
       <c r="U29" s="15" t="n">
         <v>12.49</v>
       </c>
-      <c r="V29" s="16" t="n">
+      <c r="V29" s="17" t="n">
         <v>11.51</v>
       </c>
-      <c r="W29" s="17" t="n">
+      <c r="W29" s="16" t="n">
         <v>13.16</v>
       </c>
       <c r="X29" s="18" t="n">
@@ -3011,7 +3235,7 @@
       <c r="Y29" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z29" s="21" t="inlineStr">
+      <c r="Z29" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -3025,7 +3249,7 @@
       </c>
       <c r="B30" s="20" t="inlineStr">
         <is>
-          <t>Amziane</t>
+          <t>Azri</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -3048,7 +3272,7 @@
       <c r="H30" s="15" t="n">
         <v>16.72</v>
       </c>
-      <c r="I30" s="16" t="n">
+      <c r="I30" s="17" t="n">
         <v>10.04</v>
       </c>
       <c r="J30" s="15" t="n">
@@ -3057,7 +3281,7 @@
       <c r="K30" s="15" t="n">
         <v>18.09</v>
       </c>
-      <c r="M30" s="17" t="n">
+      <c r="M30" s="16" t="n">
         <v>15.92</v>
       </c>
       <c r="N30" s="14" t="n">
@@ -3069,7 +3293,7 @@
       <c r="P30" s="15" t="n">
         <v>18.71</v>
       </c>
-      <c r="Q30" s="16" t="n">
+      <c r="Q30" s="17" t="n">
         <v>9.76</v>
       </c>
       <c r="R30" s="15" t="n">
@@ -3078,7 +3302,7 @@
       <c r="S30" s="15" t="n">
         <v>17.92</v>
       </c>
-      <c r="T30" s="16" t="n">
+      <c r="T30" s="17" t="n">
         <v>10.51</v>
       </c>
       <c r="U30" s="15" t="n">
@@ -3087,7 +3311,7 @@
       <c r="V30" s="15" t="n">
         <v>15.93</v>
       </c>
-      <c r="W30" s="17" t="n">
+      <c r="W30" s="16" t="n">
         <v>15.11</v>
       </c>
       <c r="X30" s="18" t="n">
@@ -3096,7 +3320,7 @@
       <c r="Y30" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z30" s="21" t="inlineStr">
+      <c r="Z30" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -3110,7 +3334,7 @@
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>Bensaid</t>
+          <t>Bouchta</t>
         </is>
       </c>
       <c r="C31" s="13" t="inlineStr">
@@ -3124,10 +3348,10 @@
       <c r="E31" s="15" t="n">
         <v>14.34</v>
       </c>
-      <c r="F31" s="16" t="n">
+      <c r="F31" s="17" t="n">
         <v>11.36</v>
       </c>
-      <c r="G31" s="16" t="n">
+      <c r="G31" s="17" t="n">
         <v>8.23</v>
       </c>
       <c r="H31" s="15" t="n">
@@ -3142,7 +3366,7 @@
       <c r="K31" s="15" t="n">
         <v>13.36</v>
       </c>
-      <c r="M31" s="17" t="n">
+      <c r="M31" s="16" t="n">
         <v>13.25</v>
       </c>
       <c r="N31" s="14" t="n">
@@ -3157,7 +3381,7 @@
       <c r="Q31" s="15" t="n">
         <v>16.8</v>
       </c>
-      <c r="R31" s="16" t="n">
+      <c r="R31" s="17" t="n">
         <v>7.66</v>
       </c>
       <c r="S31" s="15" t="n">
@@ -3172,7 +3396,7 @@
       <c r="V31" s="15" t="n">
         <v>17.25</v>
       </c>
-      <c r="W31" s="17" t="n">
+      <c r="W31" s="16" t="n">
         <v>14.95</v>
       </c>
       <c r="X31" s="18" t="n">
@@ -3181,7 +3405,7 @@
       <c r="Y31" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z31" s="21" t="inlineStr">
+      <c r="Z31" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -3195,7 +3419,7 @@
       </c>
       <c r="B32" s="20" t="inlineStr">
         <is>
-          <t>Chergui</t>
+          <t>Chaibi</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -3221,13 +3445,13 @@
       <c r="I32" s="15" t="n">
         <v>19.07</v>
       </c>
-      <c r="J32" s="16" t="n">
+      <c r="J32" s="17" t="n">
         <v>11.26</v>
       </c>
-      <c r="K32" s="16" t="n">
+      <c r="K32" s="17" t="n">
         <v>10.1</v>
       </c>
-      <c r="M32" s="17" t="n">
+      <c r="M32" s="16" t="n">
         <v>13.87</v>
       </c>
       <c r="N32" s="14" t="n">
@@ -3236,7 +3460,7 @@
       <c r="O32" s="15" t="n">
         <v>18.33</v>
       </c>
-      <c r="P32" s="16" t="n">
+      <c r="P32" s="17" t="n">
         <v>9.460000000000001</v>
       </c>
       <c r="Q32" s="15" t="n">
@@ -3257,7 +3481,7 @@
       <c r="V32" s="15" t="n">
         <v>13.72</v>
       </c>
-      <c r="W32" s="17" t="n">
+      <c r="W32" s="16" t="n">
         <v>14.63</v>
       </c>
       <c r="X32" s="18" t="n">
@@ -3266,7 +3490,7 @@
       <c r="Y32" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z32" s="21" t="inlineStr">
+      <c r="Z32" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -3280,7 +3504,7 @@
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>Daoudi</t>
+          <t>Derfoufi</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr">
@@ -3297,7 +3521,7 @@
       <c r="F33" s="15" t="n">
         <v>12.74</v>
       </c>
-      <c r="G33" s="16" t="n">
+      <c r="G33" s="17" t="n">
         <v>9.1</v>
       </c>
       <c r="H33" s="15" t="n">
@@ -3312,7 +3536,7 @@
       <c r="K33" s="15" t="n">
         <v>15.92</v>
       </c>
-      <c r="M33" s="17" t="n">
+      <c r="M33" s="16" t="n">
         <v>13.64</v>
       </c>
       <c r="N33" s="14" t="n">
@@ -3330,19 +3554,19 @@
       <c r="R33" s="15" t="n">
         <v>18.83</v>
       </c>
-      <c r="S33" s="16" t="n">
+      <c r="S33" s="17" t="n">
         <v>10.52</v>
       </c>
       <c r="T33" s="15" t="n">
         <v>18.62</v>
       </c>
-      <c r="U33" s="16" t="n">
+      <c r="U33" s="17" t="n">
         <v>10.2</v>
       </c>
       <c r="V33" s="15" t="n">
         <v>16.65</v>
       </c>
-      <c r="W33" s="17" t="n">
+      <c r="W33" s="16" t="n">
         <v>16.62</v>
       </c>
       <c r="X33" s="18" t="n">
@@ -3351,7 +3575,7 @@
       <c r="Y33" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z33" s="21" t="inlineStr">
+      <c r="Z33" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -3365,7 +3589,7 @@
       </c>
       <c r="B34" s="20" t="inlineStr">
         <is>
-          <t>Ettahiri</t>
+          <t>Elouafi</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
@@ -3397,13 +3621,13 @@
       <c r="K34" s="15" t="n">
         <v>16.1</v>
       </c>
-      <c r="M34" s="17" t="n">
+      <c r="M34" s="16" t="n">
         <v>15.28</v>
       </c>
       <c r="N34" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="O34" s="16" t="n">
+      <c r="O34" s="17" t="n">
         <v>11.25</v>
       </c>
       <c r="P34" s="15" t="n">
@@ -3415,10 +3639,10 @@
       <c r="R34" s="15" t="n">
         <v>18.07</v>
       </c>
-      <c r="S34" s="16" t="n">
+      <c r="S34" s="17" t="n">
         <v>10.46</v>
       </c>
-      <c r="T34" s="16" t="n">
+      <c r="T34" s="17" t="n">
         <v>11.15</v>
       </c>
       <c r="U34" s="15" t="n">
@@ -3427,7 +3651,7 @@
       <c r="V34" s="15" t="n">
         <v>14.62</v>
       </c>
-      <c r="W34" s="17" t="n">
+      <c r="W34" s="16" t="n">
         <v>13.77</v>
       </c>
       <c r="X34" s="18" t="n">
@@ -3436,7 +3660,7 @@
       <c r="Y34" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z34" s="21" t="inlineStr">
+      <c r="Z34" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -3450,7 +3674,7 @@
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>Faqir</t>
+          <t>Fekhari</t>
         </is>
       </c>
       <c r="C35" s="13" t="inlineStr">
@@ -3467,7 +3691,7 @@
       <c r="F35" s="15" t="n">
         <v>15.26</v>
       </c>
-      <c r="G35" s="16" t="n">
+      <c r="G35" s="17" t="n">
         <v>9.970000000000001</v>
       </c>
       <c r="H35" s="15" t="n">
@@ -3479,10 +3703,10 @@
       <c r="J35" s="15" t="n">
         <v>12.4</v>
       </c>
-      <c r="K35" s="16" t="n">
+      <c r="K35" s="17" t="n">
         <v>8.210000000000001</v>
       </c>
-      <c r="M35" s="17" t="n">
+      <c r="M35" s="16" t="n">
         <v>13.05</v>
       </c>
       <c r="N35" s="14" t="n">
@@ -3506,13 +3730,13 @@
       <c r="T35" s="15" t="n">
         <v>12.22</v>
       </c>
-      <c r="U35" s="16" t="n">
+      <c r="U35" s="17" t="n">
         <v>9.880000000000001</v>
       </c>
       <c r="V35" s="15" t="n">
         <v>12.48</v>
       </c>
-      <c r="W35" s="17" t="n">
+      <c r="W35" s="16" t="n">
         <v>14.46</v>
       </c>
       <c r="X35" s="18" t="n">
@@ -3521,7 +3745,7 @@
       <c r="Y35" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z35" s="21" t="inlineStr">
+      <c r="Z35" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -3535,7 +3759,7 @@
       </c>
       <c r="B36" s="20" t="inlineStr">
         <is>
-          <t>Grari</t>
+          <t>Guennouni</t>
         </is>
       </c>
       <c r="C36" s="20" t="inlineStr">
@@ -3546,7 +3770,7 @@
       <c r="D36" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="E36" s="16" t="n">
+      <c r="E36" s="17" t="n">
         <v>10.66</v>
       </c>
       <c r="F36" s="15" t="n">
@@ -3558,7 +3782,7 @@
       <c r="H36" s="15" t="n">
         <v>12.97</v>
       </c>
-      <c r="I36" s="16" t="n">
+      <c r="I36" s="17" t="n">
         <v>11.75</v>
       </c>
       <c r="J36" s="15" t="n">
@@ -3567,7 +3791,7 @@
       <c r="K36" s="15" t="n">
         <v>17.47</v>
       </c>
-      <c r="M36" s="17" t="n">
+      <c r="M36" s="16" t="n">
         <v>13.64</v>
       </c>
       <c r="N36" s="14" t="n">
@@ -3582,7 +3806,7 @@
       <c r="Q36" s="15" t="n">
         <v>13.8</v>
       </c>
-      <c r="R36" s="16" t="n">
+      <c r="R36" s="17" t="n">
         <v>11.32</v>
       </c>
       <c r="S36" s="15" t="n">
@@ -3597,7 +3821,7 @@
       <c r="V36" s="15" t="n">
         <v>12.54</v>
       </c>
-      <c r="W36" s="17" t="n">
+      <c r="W36" s="16" t="n">
         <v>14.22</v>
       </c>
       <c r="X36" s="18" t="n">
@@ -3606,7 +3830,7 @@
       <c r="Y36" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z36" s="21" t="inlineStr">
+      <c r="Z36" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -3620,7 +3844,7 @@
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>Hannioui</t>
+          <t>Hajouji</t>
         </is>
       </c>
       <c r="C37" s="13" t="inlineStr">
@@ -3640,7 +3864,7 @@
       <c r="G37" s="15" t="n">
         <v>13.46</v>
       </c>
-      <c r="H37" s="16" t="n">
+      <c r="H37" s="17" t="n">
         <v>9.35</v>
       </c>
       <c r="I37" s="15" t="n">
@@ -3652,13 +3876,13 @@
       <c r="K37" s="15" t="n">
         <v>13.92</v>
       </c>
-      <c r="M37" s="17" t="n">
+      <c r="M37" s="16" t="n">
         <v>14.62</v>
       </c>
       <c r="N37" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="O37" s="16" t="n">
+      <c r="O37" s="17" t="n">
         <v>10.02</v>
       </c>
       <c r="P37" s="15" t="n">
@@ -3676,13 +3900,13 @@
       <c r="T37" s="15" t="n">
         <v>13.52</v>
       </c>
-      <c r="U37" s="16" t="n">
+      <c r="U37" s="17" t="n">
         <v>10.23</v>
       </c>
       <c r="V37" s="15" t="n">
         <v>14.54</v>
       </c>
-      <c r="W37" s="17" t="n">
+      <c r="W37" s="16" t="n">
         <v>12.49</v>
       </c>
       <c r="X37" s="18" t="n">
@@ -3691,7 +3915,7 @@
       <c r="Y37" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z37" s="21" t="inlineStr">
+      <c r="Z37" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -3705,7 +3929,7 @@
       </c>
       <c r="B38" s="20" t="inlineStr">
         <is>
-          <t>Ibourk</t>
+          <t>Ikken</t>
         </is>
       </c>
       <c r="C38" s="20" t="inlineStr">
@@ -3725,19 +3949,19 @@
       <c r="G38" s="15" t="n">
         <v>14.85</v>
       </c>
-      <c r="H38" s="16" t="n">
+      <c r="H38" s="17" t="n">
         <v>11.55</v>
       </c>
       <c r="I38" s="15" t="n">
         <v>16.78</v>
       </c>
-      <c r="J38" s="16" t="n">
+      <c r="J38" s="17" t="n">
         <v>11.45</v>
       </c>
       <c r="K38" s="15" t="n">
         <v>19.41</v>
       </c>
-      <c r="M38" s="17" t="n">
+      <c r="M38" s="16" t="n">
         <v>15.26</v>
       </c>
       <c r="N38" s="14" t="n">
@@ -3746,7 +3970,7 @@
       <c r="O38" s="15" t="n">
         <v>14.33</v>
       </c>
-      <c r="P38" s="16" t="n">
+      <c r="P38" s="17" t="n">
         <v>11.58</v>
       </c>
       <c r="Q38" s="15" t="n">
@@ -3767,7 +3991,7 @@
       <c r="V38" s="15" t="n">
         <v>13.46</v>
       </c>
-      <c r="W38" s="17" t="n">
+      <c r="W38" s="16" t="n">
         <v>14.01</v>
       </c>
       <c r="X38" s="18" t="n">
@@ -3776,7 +4000,7 @@
       <c r="Y38" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z38" s="21" t="inlineStr">
+      <c r="Z38" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -3790,7 +4014,7 @@
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>Jabrane</t>
+          <t>Joudar</t>
         </is>
       </c>
       <c r="C39" s="13" t="inlineStr">
@@ -3801,69 +4025,69 @@
       <c r="D39" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="E39" s="15" t="n">
-        <v>12.34</v>
+      <c r="E39" s="17" t="n">
+        <v>2.9</v>
       </c>
       <c r="F39" s="15" t="n">
-        <v>15.8</v>
+        <v>12.19</v>
       </c>
       <c r="G39" s="15" t="n">
-        <v>15.84</v>
-      </c>
-      <c r="H39" s="16" t="n">
-        <v>11.08</v>
-      </c>
-      <c r="I39" s="16" t="n">
-        <v>11.84</v>
-      </c>
-      <c r="J39" s="15" t="n">
-        <v>15.35</v>
-      </c>
-      <c r="K39" s="16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="M39" s="17" t="n">
-        <v>13.52</v>
+        <v>12.23</v>
+      </c>
+      <c r="H39" s="17" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="I39" s="17" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="J39" s="17" t="n">
+        <v>11.66</v>
+      </c>
+      <c r="K39" s="17" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="M39" s="16" t="n">
+        <v>8.59</v>
       </c>
       <c r="N39" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="O39" s="15" t="n">
-        <v>12</v>
+      <c r="O39" s="17" t="n">
+        <v>7.68</v>
       </c>
       <c r="P39" s="15" t="n">
-        <v>19.23</v>
-      </c>
-      <c r="Q39" s="15" t="n">
-        <v>12.88</v>
+        <v>16.25</v>
+      </c>
+      <c r="Q39" s="17" t="n">
+        <v>8.720000000000001</v>
       </c>
       <c r="R39" s="15" t="n">
-        <v>15.83</v>
-      </c>
-      <c r="S39" s="15" t="n">
-        <v>13.41</v>
+        <v>12.22</v>
+      </c>
+      <c r="S39" s="17" t="n">
+        <v>6.32</v>
       </c>
       <c r="T39" s="15" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="U39" s="15" t="n">
-        <v>14.19</v>
-      </c>
-      <c r="V39" s="15" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="W39" s="17" t="n">
-        <v>14.96</v>
+        <v>16.45</v>
+      </c>
+      <c r="U39" s="17" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="V39" s="17" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="W39" s="16" t="n">
+        <v>9.83</v>
       </c>
       <c r="X39" s="18" t="n">
-        <v>14.24</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="Y39" s="11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Z39" s="21" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
     </row>
@@ -3885,12 +4109,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z38"/>
+  <dimension ref="A1:Z39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
@@ -3922,6 +4146,31 @@
           <t>DÉPARTEMENT GEE — GÉNIE ÉLECTRIQUE ET ÉLECTRONIQUE — DEUXIÈME ANNÉE</t>
         </is>
       </c>
+      <c r="B1" s="22" t="n"/>
+      <c r="C1" s="22" t="n"/>
+      <c r="D1" s="22" t="n"/>
+      <c r="E1" s="22" t="n"/>
+      <c r="F1" s="22" t="n"/>
+      <c r="G1" s="22" t="n"/>
+      <c r="H1" s="22" t="n"/>
+      <c r="I1" s="22" t="n"/>
+      <c r="J1" s="22" t="n"/>
+      <c r="K1" s="22" t="n"/>
+      <c r="L1" s="22" t="n"/>
+      <c r="M1" s="22" t="n"/>
+      <c r="N1" s="22" t="n"/>
+      <c r="O1" s="22" t="n"/>
+      <c r="P1" s="22" t="n"/>
+      <c r="Q1" s="22" t="n"/>
+      <c r="R1" s="22" t="n"/>
+      <c r="S1" s="22" t="n"/>
+      <c r="T1" s="22" t="n"/>
+      <c r="U1" s="22" t="n"/>
+      <c r="V1" s="22" t="n"/>
+      <c r="W1" s="22" t="n"/>
+      <c r="X1" s="22" t="n"/>
+      <c r="Y1" s="22" t="n"/>
+      <c r="Z1" s="23" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -3929,22 +4178,44 @@
           <t>Informations Générales</t>
         </is>
       </c>
+      <c r="B2" s="22" t="n"/>
+      <c r="C2" s="23" t="n"/>
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>SEMESTRE 3</t>
         </is>
       </c>
+      <c r="E2" s="22" t="n"/>
+      <c r="F2" s="22" t="n"/>
+      <c r="G2" s="22" t="n"/>
+      <c r="H2" s="22" t="n"/>
+      <c r="I2" s="22" t="n"/>
+      <c r="J2" s="22" t="n"/>
+      <c r="K2" s="22" t="n"/>
+      <c r="L2" s="22" t="n"/>
+      <c r="M2" s="23" t="n"/>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>SEMESTRE 4</t>
         </is>
       </c>
+      <c r="O2" s="22" t="n"/>
+      <c r="P2" s="22" t="n"/>
+      <c r="Q2" s="22" t="n"/>
+      <c r="R2" s="22" t="n"/>
+      <c r="S2" s="22" t="n"/>
+      <c r="T2" s="22" t="n"/>
+      <c r="U2" s="22" t="n"/>
+      <c r="V2" s="22" t="n"/>
+      <c r="W2" s="23" t="n"/>
       <c r="X2" s="2" t="n"/>
       <c r="Y2" s="2" t="n"/>
       <c r="Z2" s="2" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="3" t="n"/>
+      <c r="B3" s="22" t="n"/>
+      <c r="C3" s="23" t="n"/>
       <c r="D3" s="4" t="n"/>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -4051,12 +4322,12 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Électronique de Puissance</t>
+          <t>Automatique 2</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Automatique 2</t>
+          <t>Électronique Embarquée</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -4071,7 +4342,7 @@
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>Systèmes Embarqués</t>
+          <t>Énergie Renouvelable</t>
         </is>
       </c>
       <c r="J4" s="6" t="inlineStr">
@@ -4097,12 +4368,12 @@
       </c>
       <c r="O4" s="8" t="inlineStr">
         <is>
-          <t>Énergies Renouvelables</t>
+          <t>Commande des Machines</t>
         </is>
       </c>
       <c r="P4" s="8" t="inlineStr">
         <is>
-          <t>Commande des Machines</t>
+          <t>Instrumentation</t>
         </is>
       </c>
       <c r="Q4" s="8" t="inlineStr">
@@ -4112,12 +4383,12 @@
       </c>
       <c r="R4" s="8" t="inlineStr">
         <is>
-          <t>Instrumentation</t>
+          <t>Réseaux Électriques</t>
         </is>
       </c>
       <c r="S4" s="8" t="inlineStr">
         <is>
-          <t>Qualité et Fiabilité</t>
+          <t>Maintenance Industrielle</t>
         </is>
       </c>
       <c r="T4" s="8" t="inlineStr">
@@ -4163,75 +4434,75 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>N679117</t>
+          <t>R979220</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Bahraoui</t>
+          <t>Akhchichane</t>
         </is>
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>Nora</t>
+          <t>Youssef</t>
         </is>
       </c>
       <c r="D5" s="14" t="n">
-        <v>19</v>
-      </c>
-      <c r="E5" s="16" t="n">
-        <v>5.17</v>
-      </c>
-      <c r="F5" s="16" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="G5" s="15" t="n">
-        <v>13.1</v>
+        <v>5</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="F5" s="15" t="n">
+        <v>15.78</v>
+      </c>
+      <c r="G5" s="17" t="n">
+        <v>4.56</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="I5" s="15" t="n">
-        <v>16.69</v>
-      </c>
-      <c r="J5" s="15" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="K5" s="16" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="M5" s="17" t="n">
-        <v>10.01</v>
+        <v>16.98</v>
+      </c>
+      <c r="I5" s="17" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="J5" s="17" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="K5" s="15" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="M5" s="16" t="n">
+        <v>10.27</v>
       </c>
       <c r="N5" s="14" t="n">
-        <v>18</v>
-      </c>
-      <c r="O5" s="16" t="n">
-        <v>7.81</v>
-      </c>
-      <c r="P5" s="16" t="n">
-        <v>10.66</v>
-      </c>
-      <c r="Q5" s="15" t="n">
-        <v>13</v>
-      </c>
-      <c r="R5" s="16" t="n">
-        <v>9.34</v>
+        <v>14</v>
+      </c>
+      <c r="O5" s="15" t="n">
+        <v>12.36</v>
+      </c>
+      <c r="P5" s="15" t="n">
+        <v>12.88</v>
+      </c>
+      <c r="Q5" s="17" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="R5" s="15" t="n">
+        <v>13.11</v>
       </c>
       <c r="S5" s="15" t="n">
-        <v>13.66</v>
-      </c>
-      <c r="T5" s="16" t="n">
-        <v>8.93</v>
-      </c>
-      <c r="U5" s="16" t="n">
-        <v>11.24</v>
-      </c>
-      <c r="V5" s="15" t="n">
-        <v>13.31</v>
-      </c>
-      <c r="W5" s="17" t="n">
-        <v>11.07</v>
+        <v>12.46</v>
+      </c>
+      <c r="T5" s="17" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="U5" s="17" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="V5" s="17" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="W5" s="16" t="n">
+        <v>10.81</v>
       </c>
       <c r="X5" s="18" t="n">
         <v>10.54</v>
@@ -4239,7 +4510,7 @@
       <c r="Y5" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="Z5" s="19" t="inlineStr">
+      <c r="Z5" s="21" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
@@ -4248,83 +4519,83 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t>H358033</t>
+          <t>N679117</t>
         </is>
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>Chbihi</t>
+          <t>Benbrahim</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>Omar</t>
+          <t>Nadia</t>
         </is>
       </c>
       <c r="D6" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="E6" s="16" t="n">
-        <v>6.53</v>
-      </c>
-      <c r="F6" s="16" t="n">
-        <v>8.470000000000001</v>
+        <v>9</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="F6" s="17" t="n">
+        <v>2.48</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>15.71</v>
-      </c>
-      <c r="H6" s="16" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="I6" s="16" t="n">
-        <v>9.56</v>
-      </c>
-      <c r="J6" s="16" t="n">
-        <v>9.289999999999999</v>
-      </c>
-      <c r="K6" s="15" t="n">
-        <v>16.33</v>
-      </c>
-      <c r="M6" s="17" t="n">
-        <v>9.94</v>
+        <v>12.84</v>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I6" s="15" t="n">
+        <v>16.35</v>
+      </c>
+      <c r="J6" s="15" t="n">
+        <v>13.62</v>
+      </c>
+      <c r="K6" s="17" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="M6" s="16" t="n">
+        <v>9.81</v>
       </c>
       <c r="N6" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="O6" s="16" t="n">
-        <v>10.73</v>
-      </c>
-      <c r="P6" s="16" t="n">
-        <v>10.06</v>
-      </c>
-      <c r="Q6" s="16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="R6" s="15" t="n">
-        <v>13.33</v>
+        <v>2</v>
+      </c>
+      <c r="O6" s="17" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="P6" s="17" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="Q6" s="15" t="n">
+        <v>12.77</v>
+      </c>
+      <c r="R6" s="17" t="n">
+        <v>9.17</v>
       </c>
       <c r="S6" s="15" t="n">
-        <v>17.44</v>
-      </c>
-      <c r="T6" s="16" t="n">
-        <v>7.42</v>
-      </c>
-      <c r="U6" s="15" t="n">
-        <v>16.42</v>
-      </c>
-      <c r="V6" s="16" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W6" s="17" t="n">
-        <v>10.74</v>
+        <v>13.42</v>
+      </c>
+      <c r="T6" s="17" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="U6" s="17" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="V6" s="15" t="n">
+        <v>13.06</v>
+      </c>
+      <c r="W6" s="16" t="n">
+        <v>10.87</v>
       </c>
       <c r="X6" s="18" t="n">
         <v>10.34</v>
       </c>
       <c r="Y6" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z6" s="19" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="Z6" s="21" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
@@ -4333,83 +4604,83 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>R973043</t>
+          <t>H358033</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Daoui</t>
+          <t>Chrif</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>Samira</t>
+          <t>Omar</t>
         </is>
       </c>
       <c r="D7" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="E7" s="15" t="n">
-        <v>19.29</v>
+        <v>4</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>11.57</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="G7" s="15" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="G7" s="17" t="n">
+        <v>11.68</v>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="I7" s="15" t="n">
+        <v>12.76</v>
+      </c>
+      <c r="J7" s="15" t="n">
+        <v>12.48</v>
+      </c>
+      <c r="K7" s="15" t="n">
+        <v>12.28</v>
+      </c>
+      <c r="M7" s="16" t="n">
+        <v>12.79</v>
+      </c>
+      <c r="N7" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="O7" s="15" t="n">
+        <v>17.39</v>
+      </c>
+      <c r="P7" s="15" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="Q7" s="17" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="R7" s="15" t="n">
+        <v>12.62</v>
+      </c>
+      <c r="S7" s="15" t="n">
+        <v>14.09</v>
+      </c>
+      <c r="T7" s="15" t="n">
+        <v>16.73</v>
+      </c>
+      <c r="U7" s="15" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="V7" s="15" t="n">
+        <v>16.07</v>
+      </c>
+      <c r="W7" s="16" t="n">
         <v>14.25</v>
       </c>
-      <c r="H7" s="15" t="n">
-        <v>14.34</v>
-      </c>
-      <c r="I7" s="15" t="n">
-        <v>18.79</v>
-      </c>
-      <c r="J7" s="15" t="n">
-        <v>14.31</v>
-      </c>
-      <c r="K7" s="15" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="M7" s="17" t="n">
-        <v>15.78</v>
-      </c>
-      <c r="N7" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="O7" s="16" t="n">
-        <v>11.52</v>
-      </c>
-      <c r="P7" s="15" t="n">
-        <v>13.95</v>
-      </c>
-      <c r="Q7" s="15" t="n">
-        <v>12.21</v>
-      </c>
-      <c r="R7" s="15" t="n">
-        <v>12.12</v>
-      </c>
-      <c r="S7" s="16" t="n">
-        <v>10.77</v>
-      </c>
-      <c r="T7" s="15" t="n">
-        <v>12.45</v>
-      </c>
-      <c r="U7" s="16" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="V7" s="15" t="n">
-        <v>14.06</v>
-      </c>
-      <c r="W7" s="17" t="n">
-        <v>12.39</v>
-      </c>
       <c r="X7" s="18" t="n">
-        <v>14.09</v>
+        <v>13.52</v>
       </c>
       <c r="Y7" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z7" s="21" t="inlineStr">
+      <c r="Z7" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -4418,83 +4689,83 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>N368265</t>
+          <t>R973043</t>
         </is>
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>El Aouni</t>
+          <t>Dahak</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>Karim</t>
+          <t>Samira</t>
         </is>
       </c>
       <c r="D8" s="14" t="n">
-        <v>13</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>10.86</v>
+        <v>12</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>10.57</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>18.32</v>
+        <v>12.76</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>13.48</v>
+        <v>15.17</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>14.49</v>
+        <v>15.65</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>14.81</v>
-      </c>
-      <c r="J8" s="15" t="n">
-        <v>12.88</v>
+        <v>14.42</v>
+      </c>
+      <c r="J8" s="17" t="n">
+        <v>9.59</v>
       </c>
       <c r="K8" s="15" t="n">
-        <v>14.04</v>
-      </c>
-      <c r="M8" s="17" t="n">
-        <v>14.18</v>
+        <v>15.08</v>
+      </c>
+      <c r="M8" s="16" t="n">
+        <v>13.34</v>
       </c>
       <c r="N8" s="14" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="O8" s="15" t="n">
-        <v>16.54</v>
-      </c>
-      <c r="P8" s="16" t="n">
-        <v>10.85</v>
+        <v>18.54</v>
+      </c>
+      <c r="P8" s="15" t="n">
+        <v>14.55</v>
       </c>
       <c r="Q8" s="15" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="R8" s="15" t="n">
-        <v>17.21</v>
+        <v>14.1</v>
+      </c>
+      <c r="R8" s="17" t="n">
+        <v>8.9</v>
       </c>
       <c r="S8" s="15" t="n">
-        <v>12.53</v>
+        <v>18.98</v>
       </c>
       <c r="T8" s="15" t="n">
-        <v>19.13</v>
-      </c>
-      <c r="U8" s="16" t="n">
-        <v>11.94</v>
+        <v>19.33</v>
+      </c>
+      <c r="U8" s="15" t="n">
+        <v>16.39</v>
       </c>
       <c r="V8" s="15" t="n">
-        <v>13.15</v>
-      </c>
-      <c r="W8" s="17" t="n">
-        <v>14.79</v>
+        <v>13.97</v>
+      </c>
+      <c r="W8" s="16" t="n">
+        <v>15.43</v>
       </c>
       <c r="X8" s="18" t="n">
-        <v>14.48</v>
+        <v>14.38</v>
       </c>
       <c r="Y8" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z8" s="21" t="inlineStr">
+      <c r="Z8" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -4503,83 +4774,83 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>M674923</t>
+          <t>N368265</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>Farissi</t>
+          <t>El Boukili</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>Rim</t>
+          <t>Karim</t>
         </is>
       </c>
       <c r="D9" s="14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>13.33</v>
+        <v>13.48</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>19.18</v>
-      </c>
-      <c r="G9" s="16" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="H9" s="16" t="n">
-        <v>10.47</v>
+        <v>12.65</v>
+      </c>
+      <c r="G9" s="15" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>12.88</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>19.26</v>
+        <v>14.49</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>17.26</v>
-      </c>
-      <c r="K9" s="15" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="M9" s="17" t="n">
-        <v>14.78</v>
+        <v>16.54</v>
+      </c>
+      <c r="K9" s="17" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="M9" s="16" t="n">
+        <v>13.38</v>
       </c>
       <c r="N9" s="14" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O9" s="15" t="n">
-        <v>14.53</v>
+        <v>17.6</v>
       </c>
       <c r="P9" s="15" t="n">
-        <v>13.1</v>
+        <v>17.21</v>
       </c>
       <c r="Q9" s="15" t="n">
-        <v>14.44</v>
+        <v>12.53</v>
       </c>
       <c r="R9" s="15" t="n">
-        <v>13.58</v>
-      </c>
-      <c r="S9" s="15" t="n">
-        <v>14.48</v>
-      </c>
-      <c r="T9" s="16" t="n">
-        <v>9.99</v>
+        <v>19.13</v>
+      </c>
+      <c r="S9" s="17" t="n">
+        <v>11.94</v>
+      </c>
+      <c r="T9" s="17" t="n">
+        <v>10.18</v>
       </c>
       <c r="U9" s="15" t="n">
-        <v>13.72</v>
+        <v>15.34</v>
       </c>
       <c r="V9" s="15" t="n">
-        <v>13.65</v>
-      </c>
-      <c r="W9" s="17" t="n">
-        <v>13.59</v>
+        <v>18.66</v>
+      </c>
+      <c r="W9" s="16" t="n">
+        <v>15.61</v>
       </c>
       <c r="X9" s="18" t="n">
-        <v>14.18</v>
+        <v>14.5</v>
       </c>
       <c r="Y9" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z9" s="21" t="inlineStr">
+      <c r="Z9" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -4588,83 +4859,83 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>G867003</t>
+          <t>M674923</t>
         </is>
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Grioui</t>
+          <t>Fahr</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>Amine</t>
+          <t>Rim</t>
         </is>
       </c>
       <c r="D10" s="14" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>16.65</v>
-      </c>
-      <c r="F10" s="16" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="G10" s="15" t="n">
-        <v>17.34</v>
+        <v>19.18</v>
+      </c>
+      <c r="F10" s="17" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="G10" s="17" t="n">
+        <v>10.47</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>14.43</v>
+        <v>19.26</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>18.87</v>
+        <v>17.26</v>
       </c>
       <c r="J10" s="15" t="n">
-        <v>13.65</v>
+        <v>12.8</v>
       </c>
       <c r="K10" s="15" t="n">
-        <v>15.53</v>
-      </c>
-      <c r="M10" s="17" t="n">
-        <v>15.33</v>
+        <v>14.53</v>
+      </c>
+      <c r="M10" s="16" t="n">
+        <v>14.94</v>
       </c>
       <c r="N10" s="14" t="n">
         <v>6</v>
       </c>
       <c r="O10" s="15" t="n">
-        <v>12.81</v>
+        <v>13.72</v>
       </c>
       <c r="P10" s="15" t="n">
-        <v>12.88</v>
+        <v>14.44</v>
       </c>
       <c r="Q10" s="15" t="n">
-        <v>14.63</v>
-      </c>
-      <c r="R10" s="16" t="n">
-        <v>8.92</v>
-      </c>
-      <c r="S10" s="15" t="n">
-        <v>18.13</v>
+        <v>13.58</v>
+      </c>
+      <c r="R10" s="15" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="S10" s="17" t="n">
+        <v>9.99</v>
       </c>
       <c r="T10" s="15" t="n">
-        <v>13.24</v>
-      </c>
-      <c r="U10" s="16" t="n">
-        <v>10.14</v>
+        <v>14.48</v>
+      </c>
+      <c r="U10" s="15" t="n">
+        <v>13.1</v>
       </c>
       <c r="V10" s="15" t="n">
-        <v>17.89</v>
-      </c>
-      <c r="W10" s="17" t="n">
-        <v>13.81</v>
+        <v>13.66</v>
+      </c>
+      <c r="W10" s="16" t="n">
+        <v>13.21</v>
       </c>
       <c r="X10" s="18" t="n">
-        <v>14.57</v>
+        <v>14.07</v>
       </c>
       <c r="Y10" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z10" s="21" t="inlineStr">
+      <c r="Z10" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -4673,83 +4944,83 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>N648936</t>
+          <t>G867003</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>Hssaine</t>
+          <t>Ghazali</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>Latifa</t>
+          <t>Amine</t>
         </is>
       </c>
       <c r="D11" s="14" t="n">
-        <v>11</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>11.16</v>
-      </c>
-      <c r="F11" s="15" t="n">
-        <v>15.87</v>
-      </c>
-      <c r="G11" s="16" t="n">
-        <v>11.76</v>
+        <v>9</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>17.34</v>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>8.48</v>
+      </c>
+      <c r="G11" s="15" t="n">
+        <v>18.87</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>15.6</v>
+        <v>13.65</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>14.31</v>
+        <v>15.53</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>14.93</v>
-      </c>
-      <c r="K11" s="16" t="n">
-        <v>11.48</v>
-      </c>
-      <c r="M11" s="17" t="n">
-        <v>13.55</v>
+        <v>12.81</v>
+      </c>
+      <c r="K11" s="15" t="n">
+        <v>12.88</v>
+      </c>
+      <c r="M11" s="16" t="n">
+        <v>14.39</v>
       </c>
       <c r="N11" s="14" t="n">
         <v>12</v>
       </c>
       <c r="O11" s="15" t="n">
-        <v>18.23</v>
-      </c>
-      <c r="P11" s="15" t="n">
-        <v>13.27</v>
+        <v>13.18</v>
+      </c>
+      <c r="P11" s="17" t="n">
+        <v>8.92</v>
       </c>
       <c r="Q11" s="15" t="n">
-        <v>13.55</v>
+        <v>18.13</v>
       </c>
       <c r="R11" s="15" t="n">
+        <v>13.24</v>
+      </c>
+      <c r="S11" s="17" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="T11" s="15" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="U11" s="15" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="V11" s="15" t="n">
+        <v>17.03</v>
+      </c>
+      <c r="W11" s="16" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="X11" s="18" t="n">
         <v>14.36</v>
-      </c>
-      <c r="S11" s="15" t="n">
-        <v>14.43</v>
-      </c>
-      <c r="T11" s="15" t="n">
-        <v>13.54</v>
-      </c>
-      <c r="U11" s="15" t="n">
-        <v>12.61</v>
-      </c>
-      <c r="V11" s="15" t="n">
-        <v>13.68</v>
-      </c>
-      <c r="W11" s="17" t="n">
-        <v>14.33</v>
-      </c>
-      <c r="X11" s="18" t="n">
-        <v>13.94</v>
       </c>
       <c r="Y11" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z11" s="21" t="inlineStr">
+      <c r="Z11" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -4758,83 +5029,83 @@
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>T714533</t>
+          <t>N648936</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Idhmad</t>
+          <t>Hachimi</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>Tarik</t>
+          <t>Latifa</t>
         </is>
       </c>
       <c r="D12" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>17.74</v>
-      </c>
-      <c r="F12" s="15" t="n">
-        <v>16.83</v>
+        <v>15.87</v>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>11.76</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>12.66</v>
-      </c>
-      <c r="H12" s="16" t="n">
-        <v>11.54</v>
+        <v>15.6</v>
+      </c>
+      <c r="H12" s="15" t="n">
+        <v>13.54</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>18.03</v>
-      </c>
-      <c r="J12" s="15" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="K12" s="16" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="M12" s="17" t="n">
-        <v>15.43</v>
+        <v>13.27</v>
+      </c>
+      <c r="J12" s="17" t="n">
+        <v>11.48</v>
+      </c>
+      <c r="K12" s="15" t="n">
+        <v>18.23</v>
+      </c>
+      <c r="M12" s="16" t="n">
+        <v>14.22</v>
       </c>
       <c r="N12" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="O12" s="15" t="n">
-        <v>13.26</v>
+        <v>16</v>
+      </c>
+      <c r="O12" s="17" t="n">
+        <v>10.39</v>
       </c>
       <c r="P12" s="15" t="n">
-        <v>17.59</v>
+        <v>13.55</v>
       </c>
       <c r="Q12" s="15" t="n">
-        <v>12.6</v>
+        <v>14.31</v>
       </c>
       <c r="R12" s="15" t="n">
-        <v>13.03</v>
+        <v>14.43</v>
       </c>
       <c r="S12" s="15" t="n">
-        <v>16.81</v>
+        <v>14.93</v>
       </c>
       <c r="T12" s="15" t="n">
-        <v>13.85</v>
+        <v>12.61</v>
       </c>
       <c r="U12" s="15" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="V12" s="16" t="n">
-        <v>11.06</v>
-      </c>
-      <c r="W12" s="17" t="n">
-        <v>14.32</v>
+        <v>13.68</v>
+      </c>
+      <c r="V12" s="15" t="n">
+        <v>16.76</v>
+      </c>
+      <c r="W12" s="16" t="n">
+        <v>13.86</v>
       </c>
       <c r="X12" s="18" t="n">
-        <v>14.88</v>
+        <v>14.04</v>
       </c>
       <c r="Y12" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z12" s="21" t="inlineStr">
+      <c r="Z12" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -4843,83 +5114,83 @@
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>T505557</t>
+          <t>T714533</t>
         </is>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>Jaouad</t>
+          <t>Idali</t>
         </is>
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>Houda</t>
+          <t>Tarik</t>
         </is>
       </c>
       <c r="D13" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>14.39</v>
+        <v>17.74</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>19.38</v>
-      </c>
-      <c r="G13" s="16" t="n">
-        <v>8.66</v>
-      </c>
-      <c r="H13" s="15" t="n">
-        <v>13.72</v>
-      </c>
-      <c r="I13" s="16" t="n">
-        <v>9.869999999999999</v>
+        <v>16.83</v>
+      </c>
+      <c r="G13" s="15" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="H13" s="17" t="n">
+        <v>11.54</v>
+      </c>
+      <c r="I13" s="15" t="n">
+        <v>18.03</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>17.97</v>
-      </c>
-      <c r="K13" s="15" t="n">
-        <v>17.07</v>
-      </c>
-      <c r="M13" s="17" t="n">
-        <v>14.19</v>
+        <v>19.1</v>
+      </c>
+      <c r="K13" s="17" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="M13" s="16" t="n">
+        <v>15.43</v>
       </c>
       <c r="N13" s="14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O13" s="15" t="n">
-        <v>12.04</v>
-      </c>
-      <c r="P13" s="16" t="n">
-        <v>9.81</v>
+        <v>13.26</v>
+      </c>
+      <c r="P13" s="15" t="n">
+        <v>17.59</v>
       </c>
       <c r="Q13" s="15" t="n">
-        <v>17.66</v>
+        <v>12.6</v>
       </c>
       <c r="R13" s="15" t="n">
-        <v>12.37</v>
+        <v>13.03</v>
       </c>
       <c r="S13" s="15" t="n">
-        <v>13.91</v>
+        <v>16.81</v>
       </c>
       <c r="T13" s="15" t="n">
-        <v>16.92</v>
+        <v>13.85</v>
       </c>
       <c r="U13" s="15" t="n">
-        <v>18.24</v>
-      </c>
-      <c r="V13" s="15" t="n">
-        <v>18.33</v>
-      </c>
-      <c r="W13" s="17" t="n">
-        <v>14.7</v>
+        <v>17.8</v>
+      </c>
+      <c r="V13" s="17" t="n">
+        <v>11.06</v>
+      </c>
+      <c r="W13" s="16" t="n">
+        <v>14.32</v>
       </c>
       <c r="X13" s="18" t="n">
-        <v>14.45</v>
+        <v>14.88</v>
       </c>
       <c r="Y13" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z13" s="21" t="inlineStr">
+      <c r="Z13" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -4928,83 +5199,83 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>B523513</t>
+          <t>T505557</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Kharbouch</t>
+          <t>Jalili</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>Bilal</t>
+          <t>Houda</t>
         </is>
       </c>
       <c r="D14" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>14.39</v>
+      </c>
+      <c r="F14" s="15" t="n">
+        <v>19.38</v>
+      </c>
+      <c r="G14" s="17" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="H14" s="15" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="I14" s="17" t="n">
+        <v>9.869999999999999</v>
+      </c>
+      <c r="J14" s="15" t="n">
+        <v>17.97</v>
+      </c>
+      <c r="K14" s="15" t="n">
+        <v>17.07</v>
+      </c>
+      <c r="M14" s="16" t="n">
+        <v>14.19</v>
+      </c>
+      <c r="N14" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="15" t="n">
-        <v>12.38</v>
-      </c>
-      <c r="F14" s="15" t="n">
-        <v>14.97</v>
-      </c>
-      <c r="G14" s="16" t="n">
-        <v>11.59</v>
-      </c>
-      <c r="H14" s="15" t="n">
-        <v>12.07</v>
-      </c>
-      <c r="I14" s="15" t="n">
-        <v>16.89</v>
-      </c>
-      <c r="J14" s="16" t="n">
-        <v>10.68</v>
-      </c>
-      <c r="K14" s="15" t="n">
-        <v>12.38</v>
-      </c>
-      <c r="M14" s="17" t="n">
-        <v>13.09</v>
-      </c>
-      <c r="N14" s="14" t="n">
-        <v>19</v>
-      </c>
       <c r="O14" s="15" t="n">
-        <v>14.97</v>
-      </c>
-      <c r="P14" s="16" t="n">
-        <v>8.300000000000001</v>
+        <v>12.04</v>
+      </c>
+      <c r="P14" s="17" t="n">
+        <v>9.81</v>
       </c>
       <c r="Q14" s="15" t="n">
-        <v>18.92</v>
+        <v>17.66</v>
       </c>
       <c r="R14" s="15" t="n">
-        <v>17.89</v>
+        <v>12.37</v>
       </c>
       <c r="S14" s="15" t="n">
         <v>13.91</v>
       </c>
       <c r="T14" s="15" t="n">
-        <v>16.53</v>
+        <v>16.92</v>
       </c>
       <c r="U14" s="15" t="n">
-        <v>13.4</v>
+        <v>18.24</v>
       </c>
       <c r="V14" s="15" t="n">
-        <v>13.47</v>
-      </c>
-      <c r="W14" s="17" t="n">
-        <v>14.57</v>
+        <v>18.33</v>
+      </c>
+      <c r="W14" s="16" t="n">
+        <v>14.7</v>
       </c>
       <c r="X14" s="18" t="n">
-        <v>13.83</v>
+        <v>14.45</v>
       </c>
       <c r="Y14" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z14" s="21" t="inlineStr">
+      <c r="Z14" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -5013,83 +5284,83 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>K993987</t>
+          <t>B523513</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>Laaziri</t>
+          <t>Kaabi</t>
         </is>
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>Sara</t>
+          <t>Bilal</t>
         </is>
       </c>
       <c r="D15" s="14" t="n">
-        <v>14</v>
-      </c>
-      <c r="E15" s="16" t="n">
-        <v>11.13</v>
+        <v>1</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>12.38</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>19.39</v>
-      </c>
-      <c r="G15" s="15" t="n">
-        <v>14.06</v>
+        <v>14.97</v>
+      </c>
+      <c r="G15" s="17" t="n">
+        <v>11.59</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>14.34</v>
+        <v>12.07</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>12.81</v>
-      </c>
-      <c r="J15" s="15" t="n">
-        <v>17.45</v>
+        <v>16.89</v>
+      </c>
+      <c r="J15" s="17" t="n">
+        <v>10.68</v>
       </c>
       <c r="K15" s="15" t="n">
-        <v>17.04</v>
-      </c>
-      <c r="M15" s="17" t="n">
-        <v>15</v>
+        <v>12.38</v>
+      </c>
+      <c r="M15" s="16" t="n">
+        <v>13.09</v>
       </c>
       <c r="N15" s="14" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="O15" s="15" t="n">
-        <v>18.87</v>
-      </c>
-      <c r="P15" s="15" t="n">
-        <v>13.54</v>
+        <v>14.97</v>
+      </c>
+      <c r="P15" s="17" t="n">
+        <v>8.300000000000001</v>
       </c>
       <c r="Q15" s="15" t="n">
-        <v>18.46</v>
+        <v>18.92</v>
       </c>
       <c r="R15" s="15" t="n">
-        <v>14.06</v>
+        <v>17.89</v>
       </c>
       <c r="S15" s="15" t="n">
-        <v>12.84</v>
-      </c>
-      <c r="T15" s="16" t="n">
-        <v>10.85</v>
-      </c>
-      <c r="U15" s="16" t="n">
-        <v>10.7</v>
+        <v>13.91</v>
+      </c>
+      <c r="T15" s="15" t="n">
+        <v>16.53</v>
+      </c>
+      <c r="U15" s="15" t="n">
+        <v>13.4</v>
       </c>
       <c r="V15" s="15" t="n">
-        <v>13.03</v>
-      </c>
-      <c r="W15" s="17" t="n">
-        <v>14.46</v>
+        <v>13.47</v>
+      </c>
+      <c r="W15" s="16" t="n">
+        <v>14.57</v>
       </c>
       <c r="X15" s="18" t="n">
-        <v>14.73</v>
+        <v>13.83</v>
       </c>
       <c r="Y15" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z15" s="21" t="inlineStr">
+      <c r="Z15" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -5098,83 +5369,83 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>F129721</t>
+          <t>K993987</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Maarouf</t>
+          <t>Lagrini</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>Mehdi</t>
+          <t>Sara</t>
         </is>
       </c>
       <c r="D16" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" s="15" t="n">
-        <v>16.78</v>
-      </c>
-      <c r="F16" s="16" t="n">
-        <v>10.35</v>
+        <v>14</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>11.13</v>
+      </c>
+      <c r="F16" s="15" t="n">
+        <v>19.39</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>19.19</v>
+        <v>14.06</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>14.22</v>
+        <v>14.34</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>18.12</v>
+        <v>12.81</v>
       </c>
       <c r="J16" s="15" t="n">
-        <v>14.63</v>
+        <v>17.45</v>
       </c>
       <c r="K16" s="15" t="n">
-        <v>13.27</v>
-      </c>
-      <c r="M16" s="17" t="n">
-        <v>15.33</v>
+        <v>17.04</v>
+      </c>
+      <c r="M16" s="16" t="n">
+        <v>15</v>
       </c>
       <c r="N16" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="O16" s="15" t="n">
+        <v>18.87</v>
+      </c>
+      <c r="P16" s="15" t="n">
         <v>13.54</v>
       </c>
-      <c r="P16" s="15" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="Q16" s="16" t="n">
-        <v>11.32</v>
+      <c r="Q16" s="15" t="n">
+        <v>18.46</v>
       </c>
       <c r="R16" s="15" t="n">
-        <v>14.94</v>
-      </c>
-      <c r="S16" s="16" t="n">
-        <v>9.23</v>
-      </c>
-      <c r="T16" s="15" t="n">
-        <v>14.07</v>
-      </c>
-      <c r="U16" s="15" t="n">
-        <v>15.39</v>
+        <v>14.06</v>
+      </c>
+      <c r="S16" s="15" t="n">
+        <v>12.84</v>
+      </c>
+      <c r="T16" s="17" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="U16" s="17" t="n">
+        <v>10.7</v>
       </c>
       <c r="V16" s="15" t="n">
-        <v>13.84</v>
-      </c>
-      <c r="W16" s="17" t="n">
-        <v>12.94</v>
+        <v>13.03</v>
+      </c>
+      <c r="W16" s="16" t="n">
+        <v>14.46</v>
       </c>
       <c r="X16" s="18" t="n">
-        <v>14.13</v>
+        <v>14.73</v>
       </c>
       <c r="Y16" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z16" s="21" t="inlineStr">
+      <c r="Z16" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -5183,83 +5454,83 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>N370744</t>
+          <t>F129721</t>
         </is>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>Nasri</t>
+          <t>Mhammedi</t>
         </is>
       </c>
       <c r="C17" s="13" t="inlineStr">
         <is>
-          <t>Ghita</t>
+          <t>Mehdi</t>
         </is>
       </c>
       <c r="D17" s="14" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>15.48</v>
-      </c>
-      <c r="F17" s="16" t="n">
-        <v>10.92</v>
+        <v>16.78</v>
+      </c>
+      <c r="F17" s="17" t="n">
+        <v>10.35</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>14.02</v>
+        <v>19.19</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>13.58</v>
+        <v>14.22</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>17.8</v>
+        <v>18.12</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>17.23</v>
-      </c>
-      <c r="K17" s="16" t="n">
-        <v>11.01</v>
-      </c>
-      <c r="M17" s="17" t="n">
-        <v>14.22</v>
+        <v>14.63</v>
+      </c>
+      <c r="K17" s="15" t="n">
+        <v>13.27</v>
+      </c>
+      <c r="M17" s="16" t="n">
+        <v>15.33</v>
       </c>
       <c r="N17" s="14" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="O17" s="15" t="n">
-        <v>14.01</v>
+        <v>13.54</v>
       </c>
       <c r="P17" s="15" t="n">
-        <v>12.43</v>
-      </c>
-      <c r="Q17" s="15" t="n">
-        <v>17.51</v>
+        <v>12.25</v>
+      </c>
+      <c r="Q17" s="17" t="n">
+        <v>11.32</v>
       </c>
       <c r="R17" s="15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="S17" s="15" t="n">
-        <v>13.67</v>
-      </c>
-      <c r="T17" s="16" t="n">
-        <v>10.63</v>
+        <v>14.94</v>
+      </c>
+      <c r="S17" s="17" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="T17" s="15" t="n">
+        <v>14.07</v>
       </c>
       <c r="U17" s="15" t="n">
-        <v>14.33</v>
+        <v>15.39</v>
       </c>
       <c r="V17" s="15" t="n">
-        <v>12.38</v>
-      </c>
-      <c r="W17" s="17" t="n">
-        <v>13.57</v>
+        <v>13.84</v>
+      </c>
+      <c r="W17" s="16" t="n">
+        <v>12.94</v>
       </c>
       <c r="X17" s="18" t="n">
-        <v>13.89</v>
+        <v>14.13</v>
       </c>
       <c r="Y17" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z17" s="21" t="inlineStr">
+      <c r="Z17" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -5268,83 +5539,83 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>K600971</t>
+          <t>N370744</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Ouhmad</t>
+          <t>Nassiri</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>Ayoub</t>
+          <t>Ghita</t>
         </is>
       </c>
       <c r="D18" s="14" t="n">
-        <v>14</v>
-      </c>
-      <c r="E18" s="16" t="n">
-        <v>11.97</v>
-      </c>
-      <c r="F18" s="15" t="n">
-        <v>15.75</v>
+        <v>20</v>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>15.48</v>
+      </c>
+      <c r="F18" s="17" t="n">
+        <v>10.92</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>17.86</v>
+        <v>14.02</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>13.6</v>
+        <v>13.58</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>14.36</v>
+        <v>17.8</v>
       </c>
       <c r="J18" s="15" t="n">
-        <v>19.16</v>
-      </c>
-      <c r="K18" s="15" t="n">
-        <v>16.15</v>
-      </c>
-      <c r="M18" s="17" t="n">
-        <v>15.37</v>
+        <v>17.23</v>
+      </c>
+      <c r="K18" s="17" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="M18" s="16" t="n">
+        <v>14.22</v>
       </c>
       <c r="N18" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="O18" s="16" t="n">
-        <v>10.62</v>
+        <v>16</v>
+      </c>
+      <c r="O18" s="15" t="n">
+        <v>14.01</v>
       </c>
       <c r="P18" s="15" t="n">
-        <v>16.97</v>
-      </c>
-      <c r="Q18" s="16" t="n">
-        <v>10.92</v>
+        <v>12.43</v>
+      </c>
+      <c r="Q18" s="15" t="n">
+        <v>17.51</v>
       </c>
       <c r="R18" s="15" t="n">
-        <v>12.63</v>
+        <v>12.5</v>
       </c>
       <c r="S18" s="15" t="n">
-        <v>14.61</v>
-      </c>
-      <c r="T18" s="15" t="n">
-        <v>17.04</v>
+        <v>13.67</v>
+      </c>
+      <c r="T18" s="17" t="n">
+        <v>10.63</v>
       </c>
       <c r="U18" s="15" t="n">
-        <v>14.22</v>
+        <v>14.33</v>
       </c>
       <c r="V18" s="15" t="n">
-        <v>14.22</v>
-      </c>
-      <c r="W18" s="17" t="n">
-        <v>13.72</v>
+        <v>12.38</v>
+      </c>
+      <c r="W18" s="16" t="n">
+        <v>13.57</v>
       </c>
       <c r="X18" s="18" t="n">
-        <v>14.54</v>
+        <v>13.89</v>
       </c>
       <c r="Y18" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z18" s="21" t="inlineStr">
+      <c r="Z18" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -5353,83 +5624,83 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>H464143</t>
+          <t>K600971</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>Qajjaj</t>
+          <t>Ouad</t>
         </is>
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
-          <t>Hafsa</t>
+          <t>Ayoub</t>
         </is>
       </c>
       <c r="D19" s="14" t="n">
-        <v>17</v>
-      </c>
-      <c r="E19" s="15" t="n">
-        <v>15.1</v>
+        <v>14</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>11.97</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>16.24</v>
+        <v>15.75</v>
       </c>
       <c r="G19" s="15" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="H19" s="15" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="I19" s="15" t="n">
+        <v>14.36</v>
+      </c>
+      <c r="J19" s="15" t="n">
+        <v>19.16</v>
+      </c>
+      <c r="K19" s="15" t="n">
         <v>16.15</v>
       </c>
-      <c r="H19" s="15" t="n">
-        <v>16.27</v>
-      </c>
-      <c r="I19" s="15" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="J19" s="15" t="n">
-        <v>13.56</v>
-      </c>
-      <c r="K19" s="15" t="n">
-        <v>13.98</v>
-      </c>
-      <c r="M19" s="17" t="n">
-        <v>15.58</v>
+      <c r="M19" s="16" t="n">
+        <v>15.37</v>
       </c>
       <c r="N19" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="O19" s="15" t="n">
-        <v>13.1</v>
+        <v>5</v>
+      </c>
+      <c r="O19" s="17" t="n">
+        <v>10.62</v>
       </c>
       <c r="P19" s="15" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="Q19" s="16" t="n">
-        <v>10.05</v>
+        <v>16.97</v>
+      </c>
+      <c r="Q19" s="17" t="n">
+        <v>10.92</v>
       </c>
       <c r="R19" s="15" t="n">
-        <v>14.19</v>
+        <v>12.63</v>
       </c>
       <c r="S19" s="15" t="n">
-        <v>17.16</v>
-      </c>
-      <c r="T19" s="16" t="n">
-        <v>10.41</v>
+        <v>14.61</v>
+      </c>
+      <c r="T19" s="15" t="n">
+        <v>17.04</v>
       </c>
       <c r="U19" s="15" t="n">
-        <v>14.74</v>
-      </c>
-      <c r="V19" s="16" t="n">
-        <v>10.46</v>
-      </c>
-      <c r="W19" s="17" t="n">
-        <v>13.03</v>
+        <v>14.22</v>
+      </c>
+      <c r="V19" s="15" t="n">
+        <v>14.22</v>
+      </c>
+      <c r="W19" s="16" t="n">
+        <v>13.72</v>
       </c>
       <c r="X19" s="18" t="n">
-        <v>14.3</v>
+        <v>14.54</v>
       </c>
       <c r="Y19" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z19" s="21" t="inlineStr">
+      <c r="Z19" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -5438,83 +5709,83 @@
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>P414245</t>
+          <t>H464143</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Rkibi</t>
+          <t>Qaissi</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>Adil</t>
+          <t>Hafsa</t>
         </is>
       </c>
       <c r="D20" s="14" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>14.13</v>
+        <v>15.1</v>
       </c>
       <c r="F20" s="15" t="n">
-        <v>12.27</v>
+        <v>16.24</v>
       </c>
       <c r="G20" s="15" t="n">
-        <v>13.48</v>
+        <v>16.15</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>12.62</v>
-      </c>
-      <c r="I20" s="16" t="n">
-        <v>11.85</v>
+        <v>16.27</v>
+      </c>
+      <c r="I20" s="15" t="n">
+        <v>16.7</v>
       </c>
       <c r="J20" s="15" t="n">
-        <v>17.32</v>
+        <v>13.56</v>
       </c>
       <c r="K20" s="15" t="n">
-        <v>18.26</v>
-      </c>
-      <c r="M20" s="17" t="n">
-        <v>13.93</v>
+        <v>13.98</v>
+      </c>
+      <c r="M20" s="16" t="n">
+        <v>15.58</v>
       </c>
       <c r="N20" s="14" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="O20" s="15" t="n">
-        <v>14.92</v>
+        <v>13.1</v>
       </c>
       <c r="P20" s="15" t="n">
-        <v>14.71</v>
-      </c>
-      <c r="Q20" s="15" t="n">
-        <v>14.53</v>
+        <v>14.8</v>
+      </c>
+      <c r="Q20" s="17" t="n">
+        <v>10.05</v>
       </c>
       <c r="R20" s="15" t="n">
-        <v>14.9</v>
+        <v>14.19</v>
       </c>
       <c r="S20" s="15" t="n">
-        <v>19.32</v>
-      </c>
-      <c r="T20" s="16" t="n">
-        <v>11.93</v>
+        <v>17.16</v>
+      </c>
+      <c r="T20" s="17" t="n">
+        <v>10.41</v>
       </c>
       <c r="U20" s="15" t="n">
-        <v>13.38</v>
-      </c>
-      <c r="V20" s="16" t="n">
-        <v>11.64</v>
-      </c>
-      <c r="W20" s="17" t="n">
-        <v>14.46</v>
+        <v>14.74</v>
+      </c>
+      <c r="V20" s="17" t="n">
+        <v>10.46</v>
+      </c>
+      <c r="W20" s="16" t="n">
+        <v>13.03</v>
       </c>
       <c r="X20" s="18" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="Y20" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z20" s="21" t="inlineStr">
+      <c r="Z20" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -5523,83 +5794,83 @@
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>T570857</t>
+          <t>P414245</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>Sabri</t>
+          <t>Regragui</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>Meriem</t>
+          <t>Adil</t>
         </is>
       </c>
       <c r="D21" s="14" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>17.4</v>
+        <v>14.13</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>15.97</v>
-      </c>
-      <c r="G21" s="16" t="n">
-        <v>11.42</v>
+        <v>12.27</v>
+      </c>
+      <c r="G21" s="15" t="n">
+        <v>13.48</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>15.61</v>
-      </c>
-      <c r="I21" s="15" t="n">
-        <v>15.49</v>
+        <v>12.62</v>
+      </c>
+      <c r="I21" s="17" t="n">
+        <v>11.85</v>
       </c>
       <c r="J21" s="15" t="n">
+        <v>17.32</v>
+      </c>
+      <c r="K21" s="15" t="n">
+        <v>18.26</v>
+      </c>
+      <c r="M21" s="16" t="n">
+        <v>13.93</v>
+      </c>
+      <c r="N21" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="O21" s="15" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="P21" s="15" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="Q21" s="15" t="n">
+        <v>14.53</v>
+      </c>
+      <c r="R21" s="15" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="S21" s="15" t="n">
+        <v>19.32</v>
+      </c>
+      <c r="T21" s="17" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="U21" s="15" t="n">
+        <v>13.38</v>
+      </c>
+      <c r="V21" s="17" t="n">
+        <v>11.64</v>
+      </c>
+      <c r="W21" s="16" t="n">
+        <v>14.46</v>
+      </c>
+      <c r="X21" s="18" t="n">
         <v>14.2</v>
-      </c>
-      <c r="K21" s="15" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="M21" s="17" t="n">
-        <v>14.94</v>
-      </c>
-      <c r="N21" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="O21" s="15" t="n">
-        <v>14.93</v>
-      </c>
-      <c r="P21" s="15" t="n">
-        <v>18.92</v>
-      </c>
-      <c r="Q21" s="15" t="n">
-        <v>13.82</v>
-      </c>
-      <c r="R21" s="16" t="n">
-        <v>10.84</v>
-      </c>
-      <c r="S21" s="15" t="n">
-        <v>15.49</v>
-      </c>
-      <c r="T21" s="16" t="n">
-        <v>9.17</v>
-      </c>
-      <c r="U21" s="15" t="n">
-        <v>18.64</v>
-      </c>
-      <c r="V21" s="15" t="n">
-        <v>16.12</v>
-      </c>
-      <c r="W21" s="17" t="n">
-        <v>14.93</v>
-      </c>
-      <c r="X21" s="18" t="n">
-        <v>14.93</v>
       </c>
       <c r="Y21" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z21" s="21" t="inlineStr">
+      <c r="Z21" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -5608,83 +5879,83 @@
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>R901405</t>
+          <t>T570857</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Toufiq</t>
+          <t>Sekkat</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>Driss</t>
+          <t>Meriem</t>
         </is>
       </c>
       <c r="D22" s="14" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>17.94</v>
-      </c>
-      <c r="F22" s="16" t="n">
-        <v>10.24</v>
-      </c>
-      <c r="G22" s="15" t="n">
-        <v>14.38</v>
+        <v>17.4</v>
+      </c>
+      <c r="F22" s="15" t="n">
+        <v>15.97</v>
+      </c>
+      <c r="G22" s="17" t="n">
+        <v>11.42</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>17.35</v>
+        <v>15.61</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>13.15</v>
+        <v>15.49</v>
       </c>
       <c r="J22" s="15" t="n">
-        <v>16.81</v>
+        <v>14.2</v>
       </c>
       <c r="K22" s="15" t="n">
-        <v>13.08</v>
-      </c>
-      <c r="M22" s="17" t="n">
-        <v>14.64</v>
+        <v>14.1</v>
+      </c>
+      <c r="M22" s="16" t="n">
+        <v>14.94</v>
       </c>
       <c r="N22" s="14" t="n">
-        <v>9</v>
-      </c>
-      <c r="O22" s="16" t="n">
-        <v>9.91</v>
-      </c>
-      <c r="P22" s="16" t="n">
-        <v>9.59</v>
+        <v>6</v>
+      </c>
+      <c r="O22" s="15" t="n">
+        <v>14.93</v>
+      </c>
+      <c r="P22" s="15" t="n">
+        <v>18.92</v>
       </c>
       <c r="Q22" s="15" t="n">
-        <v>12.94</v>
-      </c>
-      <c r="R22" s="15" t="n">
-        <v>17.59</v>
+        <v>13.82</v>
+      </c>
+      <c r="R22" s="17" t="n">
+        <v>10.84</v>
       </c>
       <c r="S22" s="15" t="n">
-        <v>12.89</v>
-      </c>
-      <c r="T22" s="15" t="n">
-        <v>16.86</v>
+        <v>15.49</v>
+      </c>
+      <c r="T22" s="17" t="n">
+        <v>9.17</v>
       </c>
       <c r="U22" s="15" t="n">
-        <v>13.68</v>
+        <v>18.64</v>
       </c>
       <c r="V22" s="15" t="n">
-        <v>13.88</v>
-      </c>
-      <c r="W22" s="17" t="n">
-        <v>13.09</v>
+        <v>16.12</v>
+      </c>
+      <c r="W22" s="16" t="n">
+        <v>14.93</v>
       </c>
       <c r="X22" s="18" t="n">
-        <v>13.87</v>
+        <v>14.93</v>
       </c>
       <c r="Y22" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z22" s="21" t="inlineStr">
+      <c r="Z22" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -5693,83 +5964,83 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>K559446</t>
+          <t>R901405</t>
         </is>
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>Uakkas</t>
+          <t>Tahri</t>
         </is>
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>Widad</t>
+          <t>Driss</t>
         </is>
       </c>
       <c r="D23" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="16" t="n">
-        <v>11.46</v>
-      </c>
-      <c r="F23" s="15" t="n">
-        <v>13.16</v>
+        <v>15</v>
+      </c>
+      <c r="E23" s="15" t="n">
+        <v>17.94</v>
+      </c>
+      <c r="F23" s="17" t="n">
+        <v>10.24</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>13.9</v>
+        <v>14.38</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>12.66</v>
-      </c>
-      <c r="I23" s="16" t="n">
-        <v>11.19</v>
+        <v>17.35</v>
+      </c>
+      <c r="I23" s="15" t="n">
+        <v>13.15</v>
       </c>
       <c r="J23" s="15" t="n">
-        <v>13.31</v>
+        <v>16.81</v>
       </c>
       <c r="K23" s="15" t="n">
-        <v>12.65</v>
-      </c>
-      <c r="M23" s="17" t="n">
-        <v>12.62</v>
+        <v>13.08</v>
+      </c>
+      <c r="M23" s="16" t="n">
+        <v>14.64</v>
       </c>
       <c r="N23" s="14" t="n">
-        <v>11</v>
-      </c>
-      <c r="O23" s="15" t="n">
-        <v>14.19</v>
-      </c>
-      <c r="P23" s="16" t="n">
-        <v>10.76</v>
+        <v>9</v>
+      </c>
+      <c r="O23" s="17" t="n">
+        <v>9.91</v>
+      </c>
+      <c r="P23" s="17" t="n">
+        <v>9.59</v>
       </c>
       <c r="Q23" s="15" t="n">
-        <v>16.29</v>
+        <v>12.94</v>
       </c>
       <c r="R23" s="15" t="n">
-        <v>14.73</v>
+        <v>17.59</v>
       </c>
       <c r="S23" s="15" t="n">
-        <v>14.26</v>
+        <v>12.89</v>
       </c>
       <c r="T23" s="15" t="n">
-        <v>13.13</v>
+        <v>16.86</v>
       </c>
       <c r="U23" s="15" t="n">
-        <v>14.48</v>
+        <v>13.68</v>
       </c>
       <c r="V23" s="15" t="n">
-        <v>14.82</v>
-      </c>
-      <c r="W23" s="17" t="n">
-        <v>14.09</v>
+        <v>13.88</v>
+      </c>
+      <c r="W23" s="16" t="n">
+        <v>13.09</v>
       </c>
       <c r="X23" s="18" t="n">
-        <v>13.36</v>
+        <v>13.87</v>
       </c>
       <c r="Y23" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z23" s="21" t="inlineStr">
+      <c r="Z23" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -5778,83 +6049,83 @@
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>H592958</t>
+          <t>K559446</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Venditti</t>
+          <t>Ufkir</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>Hamza</t>
+          <t>Widad</t>
         </is>
       </c>
       <c r="D24" s="14" t="n">
-        <v>19</v>
-      </c>
-      <c r="E24" s="16" t="n">
-        <v>11.01</v>
-      </c>
-      <c r="F24" s="16" t="n">
-        <v>9.789999999999999</v>
+        <v>0</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>11.46</v>
+      </c>
+      <c r="F24" s="15" t="n">
+        <v>13.16</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>14.71</v>
+        <v>13.9</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="I24" s="15" t="n">
-        <v>14.75</v>
+        <v>12.66</v>
+      </c>
+      <c r="I24" s="17" t="n">
+        <v>11.19</v>
       </c>
       <c r="J24" s="15" t="n">
-        <v>14.36</v>
+        <v>13.31</v>
       </c>
       <c r="K24" s="15" t="n">
-        <v>12.14</v>
-      </c>
-      <c r="M24" s="17" t="n">
         <v>12.65</v>
       </c>
+      <c r="M24" s="16" t="n">
+        <v>12.62</v>
+      </c>
       <c r="N24" s="14" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="O24" s="15" t="n">
-        <v>18.84</v>
-      </c>
-      <c r="P24" s="15" t="n">
-        <v>14.62</v>
-      </c>
-      <c r="Q24" s="16" t="n">
-        <v>10.9</v>
+        <v>14.19</v>
+      </c>
+      <c r="P24" s="17" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="Q24" s="15" t="n">
+        <v>16.29</v>
       </c>
       <c r="R24" s="15" t="n">
-        <v>14.52</v>
+        <v>14.73</v>
       </c>
       <c r="S24" s="15" t="n">
-        <v>13.12</v>
+        <v>14.26</v>
       </c>
       <c r="T24" s="15" t="n">
-        <v>14.29</v>
+        <v>13.13</v>
       </c>
       <c r="U24" s="15" t="n">
-        <v>16.11</v>
+        <v>14.48</v>
       </c>
       <c r="V24" s="15" t="n">
-        <v>12.55</v>
-      </c>
-      <c r="W24" s="17" t="n">
-        <v>14.3</v>
+        <v>14.82</v>
+      </c>
+      <c r="W24" s="16" t="n">
+        <v>14.09</v>
       </c>
       <c r="X24" s="18" t="n">
-        <v>13.48</v>
+        <v>13.36</v>
       </c>
       <c r="Y24" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z24" s="21" t="inlineStr">
+      <c r="Z24" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -5863,83 +6134,83 @@
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>K163546</t>
+          <t>H592958</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>Wahnou</t>
+          <t>Vantomme</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>Chaimaa</t>
+          <t>Hamza</t>
         </is>
       </c>
       <c r="D25" s="14" t="n">
-        <v>18</v>
-      </c>
-      <c r="E25" s="15" t="n">
-        <v>13.38</v>
-      </c>
-      <c r="F25" s="16" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="G25" s="16" t="n">
-        <v>11.32</v>
+        <v>19</v>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="F25" s="17" t="n">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="G25" s="15" t="n">
+        <v>14.71</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>15.21</v>
+        <v>12.7</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>17.49</v>
+        <v>14.75</v>
       </c>
       <c r="J25" s="15" t="n">
-        <v>16.22</v>
+        <v>14.36</v>
       </c>
       <c r="K25" s="15" t="n">
-        <v>16.69</v>
-      </c>
-      <c r="M25" s="17" t="n">
-        <v>14.14</v>
+        <v>12.14</v>
+      </c>
+      <c r="M25" s="16" t="n">
+        <v>12.65</v>
       </c>
       <c r="N25" s="14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O25" s="15" t="n">
-        <v>13.75</v>
+        <v>18.84</v>
       </c>
       <c r="P25" s="15" t="n">
-        <v>13.38</v>
-      </c>
-      <c r="Q25" s="15" t="n">
-        <v>15.91</v>
+        <v>14.62</v>
+      </c>
+      <c r="Q25" s="17" t="n">
+        <v>10.9</v>
       </c>
       <c r="R25" s="15" t="n">
-        <v>12.59</v>
-      </c>
-      <c r="S25" s="16" t="n">
-        <v>11.66</v>
+        <v>14.52</v>
+      </c>
+      <c r="S25" s="15" t="n">
+        <v>13.12</v>
       </c>
       <c r="T25" s="15" t="n">
-        <v>14.17</v>
+        <v>14.29</v>
       </c>
       <c r="U25" s="15" t="n">
-        <v>19.13</v>
+        <v>16.11</v>
       </c>
       <c r="V25" s="15" t="n">
-        <v>17.33</v>
-      </c>
-      <c r="W25" s="17" t="n">
-        <v>14.67</v>
+        <v>12.55</v>
+      </c>
+      <c r="W25" s="16" t="n">
+        <v>14.3</v>
       </c>
       <c r="X25" s="18" t="n">
-        <v>14.41</v>
+        <v>13.48</v>
       </c>
       <c r="Y25" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z25" s="21" t="inlineStr">
+      <c r="Z25" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -5948,83 +6219,83 @@
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>F964255</t>
+          <t>K163546</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Xarfi</t>
+          <t>Wardi</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>Zakaria</t>
+          <t>Chaimaa</t>
         </is>
       </c>
       <c r="D26" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="E26" s="15" t="n">
+        <v>13.38</v>
+      </c>
+      <c r="F26" s="17" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="G26" s="17" t="n">
+        <v>11.32</v>
+      </c>
+      <c r="H26" s="15" t="n">
+        <v>15.21</v>
+      </c>
+      <c r="I26" s="15" t="n">
+        <v>17.49</v>
+      </c>
+      <c r="J26" s="15" t="n">
+        <v>16.22</v>
+      </c>
+      <c r="K26" s="15" t="n">
+        <v>16.69</v>
+      </c>
+      <c r="M26" s="16" t="n">
+        <v>14.14</v>
+      </c>
+      <c r="N26" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="E26" s="16" t="n">
-        <v>11.32</v>
-      </c>
-      <c r="F26" s="15" t="n">
-        <v>16.31</v>
-      </c>
-      <c r="G26" s="15" t="n">
-        <v>14.48</v>
-      </c>
-      <c r="H26" s="15" t="n">
-        <v>19.46</v>
-      </c>
-      <c r="I26" s="15" t="n">
-        <v>13.45</v>
-      </c>
-      <c r="J26" s="15" t="n">
-        <v>18.04</v>
-      </c>
-      <c r="K26" s="15" t="n">
-        <v>17.72</v>
-      </c>
-      <c r="M26" s="17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="N26" s="14" t="n">
-        <v>2</v>
-      </c>
       <c r="O26" s="15" t="n">
-        <v>13.83</v>
-      </c>
-      <c r="P26" s="16" t="n">
-        <v>10.72</v>
+        <v>13.75</v>
+      </c>
+      <c r="P26" s="15" t="n">
+        <v>13.38</v>
       </c>
       <c r="Q26" s="15" t="n">
-        <v>12.37</v>
+        <v>15.91</v>
       </c>
       <c r="R26" s="15" t="n">
-        <v>17.57</v>
-      </c>
-      <c r="S26" s="15" t="n">
-        <v>17.66</v>
-      </c>
-      <c r="T26" s="16" t="n">
-        <v>11.13</v>
+        <v>12.59</v>
+      </c>
+      <c r="S26" s="17" t="n">
+        <v>11.66</v>
+      </c>
+      <c r="T26" s="15" t="n">
+        <v>14.17</v>
       </c>
       <c r="U26" s="15" t="n">
-        <v>19.15</v>
+        <v>19.13</v>
       </c>
       <c r="V26" s="15" t="n">
-        <v>12.26</v>
-      </c>
-      <c r="W26" s="17" t="n">
-        <v>14.05</v>
+        <v>17.33</v>
+      </c>
+      <c r="W26" s="16" t="n">
+        <v>14.67</v>
       </c>
       <c r="X26" s="18" t="n">
-        <v>14.78</v>
+        <v>14.41</v>
       </c>
       <c r="Y26" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z26" s="21" t="inlineStr">
+      <c r="Z26" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -6033,83 +6304,83 @@
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>P212869</t>
+          <t>F964255</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>Yaakoubi</t>
+          <t>Xarfi</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>Fatima</t>
+          <t>Zakaria</t>
         </is>
       </c>
       <c r="D27" s="14" t="n">
-        <v>18</v>
-      </c>
-      <c r="E27" s="16" t="n">
-        <v>11.72</v>
+        <v>7</v>
+      </c>
+      <c r="E27" s="17" t="n">
+        <v>11.32</v>
       </c>
       <c r="F27" s="15" t="n">
-        <v>16.45</v>
+        <v>16.31</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>12.16</v>
+        <v>14.48</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>14.15</v>
+        <v>19.46</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>18.98</v>
+        <v>13.45</v>
       </c>
       <c r="J27" s="15" t="n">
-        <v>14.34</v>
-      </c>
-      <c r="K27" s="16" t="n">
-        <v>11.45</v>
-      </c>
-      <c r="M27" s="17" t="n">
-        <v>14.19</v>
+        <v>18.04</v>
+      </c>
+      <c r="K27" s="15" t="n">
+        <v>17.72</v>
+      </c>
+      <c r="M27" s="16" t="n">
+        <v>15.5</v>
       </c>
       <c r="N27" s="14" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="O27" s="15" t="n">
-        <v>15.93</v>
-      </c>
-      <c r="P27" s="16" t="n">
-        <v>10.2</v>
+        <v>13.83</v>
+      </c>
+      <c r="P27" s="17" t="n">
+        <v>10.72</v>
       </c>
       <c r="Q27" s="15" t="n">
-        <v>18.72</v>
+        <v>12.37</v>
       </c>
       <c r="R27" s="15" t="n">
-        <v>12.57</v>
+        <v>17.57</v>
       </c>
       <c r="S27" s="15" t="n">
-        <v>13.01</v>
-      </c>
-      <c r="T27" s="15" t="n">
-        <v>19.18</v>
+        <v>17.66</v>
+      </c>
+      <c r="T27" s="17" t="n">
+        <v>11.13</v>
       </c>
       <c r="U27" s="15" t="n">
-        <v>15.62</v>
+        <v>19.15</v>
       </c>
       <c r="V27" s="15" t="n">
-        <v>14.99</v>
-      </c>
-      <c r="W27" s="17" t="n">
-        <v>14.88</v>
+        <v>12.26</v>
+      </c>
+      <c r="W27" s="16" t="n">
+        <v>14.05</v>
       </c>
       <c r="X27" s="18" t="n">
-        <v>14.54</v>
+        <v>14.78</v>
       </c>
       <c r="Y27" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z27" s="21" t="inlineStr">
+      <c r="Z27" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -6118,83 +6389,83 @@
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>H675934</t>
+          <t>P212869</t>
         </is>
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Zarhoun</t>
+          <t>Yatribi</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>Saad</t>
+          <t>Fatima</t>
         </is>
       </c>
       <c r="D28" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="E28" s="15" t="n">
-        <v>16.01</v>
+        <v>18</v>
+      </c>
+      <c r="E28" s="17" t="n">
+        <v>11.72</v>
       </c>
       <c r="F28" s="15" t="n">
-        <v>12.35</v>
+        <v>16.45</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>18.96</v>
+        <v>12.16</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>14.44</v>
+        <v>14.15</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>17.97</v>
+        <v>18.98</v>
       </c>
       <c r="J28" s="15" t="n">
-        <v>16.75</v>
-      </c>
-      <c r="K28" s="15" t="n">
-        <v>12.08</v>
-      </c>
-      <c r="M28" s="17" t="n">
-        <v>15.61</v>
+        <v>14.34</v>
+      </c>
+      <c r="K28" s="17" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="M28" s="16" t="n">
+        <v>14.19</v>
       </c>
       <c r="N28" s="14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O28" s="15" t="n">
-        <v>16.98</v>
-      </c>
-      <c r="P28" s="15" t="n">
-        <v>16.32</v>
-      </c>
-      <c r="Q28" s="16" t="n">
-        <v>8.18</v>
+        <v>15.93</v>
+      </c>
+      <c r="P28" s="17" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="Q28" s="15" t="n">
+        <v>18.72</v>
       </c>
       <c r="R28" s="15" t="n">
-        <v>14.02</v>
+        <v>12.57</v>
       </c>
       <c r="S28" s="15" t="n">
-        <v>15.02</v>
-      </c>
-      <c r="T28" s="16" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="U28" s="16" t="n">
-        <v>10.63</v>
+        <v>13.01</v>
+      </c>
+      <c r="T28" s="15" t="n">
+        <v>19.18</v>
+      </c>
+      <c r="U28" s="15" t="n">
+        <v>15.62</v>
       </c>
       <c r="V28" s="15" t="n">
-        <v>14.47</v>
-      </c>
-      <c r="W28" s="17" t="n">
-        <v>13.3</v>
+        <v>14.99</v>
+      </c>
+      <c r="W28" s="16" t="n">
+        <v>14.88</v>
       </c>
       <c r="X28" s="18" t="n">
-        <v>14.46</v>
+        <v>14.54</v>
       </c>
       <c r="Y28" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z28" s="21" t="inlineStr">
+      <c r="Z28" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -6203,83 +6474,83 @@
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="13" t="inlineStr">
         <is>
-          <t>G116985</t>
+          <t>H675934</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>Amziane</t>
+          <t>Ziani</t>
         </is>
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>Basma</t>
+          <t>Saad</t>
         </is>
       </c>
       <c r="D29" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>13.87</v>
+        <v>16.01</v>
       </c>
       <c r="F29" s="15" t="n">
-        <v>12.2</v>
+        <v>12.35</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>17.42</v>
-      </c>
-      <c r="H29" s="16" t="n">
-        <v>9.140000000000001</v>
+        <v>18.96</v>
+      </c>
+      <c r="H29" s="15" t="n">
+        <v>14.44</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>16.22</v>
+        <v>17.97</v>
       </c>
       <c r="J29" s="15" t="n">
-        <v>17.59</v>
+        <v>16.75</v>
       </c>
       <c r="K29" s="15" t="n">
-        <v>12.85</v>
-      </c>
-      <c r="M29" s="17" t="n">
-        <v>14.15</v>
+        <v>12.08</v>
+      </c>
+      <c r="M29" s="16" t="n">
+        <v>15.61</v>
       </c>
       <c r="N29" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O29" s="15" t="n">
-        <v>19.09</v>
+        <v>16.98</v>
       </c>
       <c r="P29" s="15" t="n">
-        <v>12.46</v>
-      </c>
-      <c r="Q29" s="16" t="n">
-        <v>8.26</v>
+        <v>16.32</v>
+      </c>
+      <c r="Q29" s="17" t="n">
+        <v>8.18</v>
       </c>
       <c r="R29" s="15" t="n">
-        <v>14.52</v>
+        <v>14.02</v>
       </c>
       <c r="S29" s="15" t="n">
-        <v>12.96</v>
-      </c>
-      <c r="T29" s="15" t="n">
-        <v>15.64</v>
-      </c>
-      <c r="U29" s="16" t="n">
-        <v>9.630000000000001</v>
+        <v>15.02</v>
+      </c>
+      <c r="T29" s="17" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="U29" s="17" t="n">
+        <v>10.63</v>
       </c>
       <c r="V29" s="15" t="n">
-        <v>17.47</v>
-      </c>
-      <c r="W29" s="17" t="n">
-        <v>13.89</v>
+        <v>14.47</v>
+      </c>
+      <c r="W29" s="16" t="n">
+        <v>13.3</v>
       </c>
       <c r="X29" s="18" t="n">
-        <v>14.02</v>
+        <v>14.46</v>
       </c>
       <c r="Y29" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z29" s="21" t="inlineStr">
+      <c r="Z29" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -6288,83 +6559,83 @@
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>M535134</t>
+          <t>G116985</t>
         </is>
       </c>
       <c r="B30" s="20" t="inlineStr">
         <is>
-          <t>Bensaid</t>
+          <t>Azri</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
         <is>
-          <t>Othmane</t>
+          <t>Basma</t>
         </is>
       </c>
       <c r="D30" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="E30" s="15" t="n">
+        <v>13.87</v>
+      </c>
+      <c r="F30" s="15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="G30" s="15" t="n">
+        <v>17.42</v>
+      </c>
+      <c r="H30" s="17" t="n">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="I30" s="15" t="n">
+        <v>16.22</v>
+      </c>
+      <c r="J30" s="15" t="n">
+        <v>17.59</v>
+      </c>
+      <c r="K30" s="15" t="n">
+        <v>12.85</v>
+      </c>
+      <c r="M30" s="16" t="n">
+        <v>14.15</v>
+      </c>
+      <c r="N30" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="E30" s="15" t="n">
-        <v>19.34</v>
-      </c>
-      <c r="F30" s="15" t="n">
-        <v>14.83</v>
-      </c>
-      <c r="G30" s="15" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="H30" s="15" t="n">
-        <v>12.98</v>
-      </c>
-      <c r="I30" s="15" t="n">
-        <v>16.31</v>
-      </c>
-      <c r="J30" s="15" t="n">
-        <v>14.95</v>
-      </c>
-      <c r="K30" s="15" t="n">
-        <v>14.42</v>
-      </c>
-      <c r="M30" s="17" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="N30" s="14" t="n">
-        <v>17</v>
-      </c>
-      <c r="O30" s="16" t="n">
-        <v>11.51</v>
+      <c r="O30" s="15" t="n">
+        <v>19.09</v>
       </c>
       <c r="P30" s="15" t="n">
-        <v>17.34</v>
-      </c>
-      <c r="Q30" s="16" t="n">
-        <v>11.81</v>
+        <v>12.46</v>
+      </c>
+      <c r="Q30" s="17" t="n">
+        <v>8.26</v>
       </c>
       <c r="R30" s="15" t="n">
-        <v>16.87</v>
+        <v>14.52</v>
       </c>
       <c r="S30" s="15" t="n">
-        <v>19.34</v>
-      </c>
-      <c r="T30" s="16" t="n">
-        <v>11.48</v>
-      </c>
-      <c r="U30" s="15" t="n">
-        <v>14.9</v>
+        <v>12.96</v>
+      </c>
+      <c r="T30" s="15" t="n">
+        <v>15.64</v>
+      </c>
+      <c r="U30" s="17" t="n">
+        <v>9.630000000000001</v>
       </c>
       <c r="V30" s="15" t="n">
-        <v>19.44</v>
-      </c>
-      <c r="W30" s="17" t="n">
-        <v>15.43</v>
+        <v>17.47</v>
+      </c>
+      <c r="W30" s="16" t="n">
+        <v>13.89</v>
       </c>
       <c r="X30" s="18" t="n">
-        <v>15.41</v>
+        <v>14.02</v>
       </c>
       <c r="Y30" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z30" s="21" t="inlineStr">
+      <c r="Z30" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -6373,83 +6644,83 @@
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="13" t="inlineStr">
         <is>
-          <t>R487780</t>
+          <t>M535134</t>
         </is>
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>Chergui</t>
+          <t>Bouchta</t>
         </is>
       </c>
       <c r="C31" s="13" t="inlineStr">
         <is>
-          <t>Sanae</t>
+          <t>Othmane</t>
         </is>
       </c>
       <c r="D31" s="14" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E31" s="15" t="n">
-        <v>16.86</v>
+        <v>19.34</v>
       </c>
       <c r="F31" s="15" t="n">
-        <v>14.88</v>
+        <v>14.83</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>17.52</v>
+        <v>14.1</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>13.51</v>
-      </c>
-      <c r="I31" s="16" t="n">
-        <v>10.59</v>
+        <v>12.98</v>
+      </c>
+      <c r="I31" s="15" t="n">
+        <v>16.31</v>
       </c>
       <c r="J31" s="15" t="n">
-        <v>14.77</v>
-      </c>
-      <c r="K31" s="16" t="n">
-        <v>10.68</v>
-      </c>
-      <c r="M31" s="17" t="n">
-        <v>14.45</v>
+        <v>14.95</v>
+      </c>
+      <c r="K31" s="15" t="n">
+        <v>14.42</v>
+      </c>
+      <c r="M31" s="16" t="n">
+        <v>15.4</v>
       </c>
       <c r="N31" s="14" t="n">
-        <v>20</v>
-      </c>
-      <c r="O31" s="15" t="n">
-        <v>14.12</v>
-      </c>
-      <c r="P31" s="16" t="n">
-        <v>10.48</v>
-      </c>
-      <c r="Q31" s="15" t="n">
-        <v>13.9</v>
+        <v>17</v>
+      </c>
+      <c r="O31" s="17" t="n">
+        <v>11.51</v>
+      </c>
+      <c r="P31" s="15" t="n">
+        <v>17.34</v>
+      </c>
+      <c r="Q31" s="17" t="n">
+        <v>11.81</v>
       </c>
       <c r="R31" s="15" t="n">
-        <v>16.58</v>
+        <v>16.87</v>
       </c>
       <c r="S31" s="15" t="n">
-        <v>14.24</v>
-      </c>
-      <c r="T31" s="15" t="n">
-        <v>12.56</v>
+        <v>19.34</v>
+      </c>
+      <c r="T31" s="17" t="n">
+        <v>11.48</v>
       </c>
       <c r="U31" s="15" t="n">
-        <v>14.98</v>
+        <v>14.9</v>
       </c>
       <c r="V31" s="15" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="W31" s="17" t="n">
-        <v>14.03</v>
+        <v>19.44</v>
+      </c>
+      <c r="W31" s="16" t="n">
+        <v>15.43</v>
       </c>
       <c r="X31" s="18" t="n">
-        <v>14.24</v>
+        <v>15.41</v>
       </c>
       <c r="Y31" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z31" s="21" t="inlineStr">
+      <c r="Z31" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -6458,83 +6729,83 @@
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>F608380</t>
+          <t>R487780</t>
         </is>
       </c>
       <c r="B32" s="20" t="inlineStr">
         <is>
-          <t>Daoudi</t>
+          <t>Chaibi</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
         <is>
-          <t>Khalid</t>
+          <t>Sanae</t>
         </is>
       </c>
       <c r="D32" s="14" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E32" s="15" t="n">
-        <v>13.47</v>
+        <v>16.86</v>
       </c>
       <c r="F32" s="15" t="n">
-        <v>12.92</v>
+        <v>14.88</v>
       </c>
       <c r="G32" s="15" t="n">
-        <v>14.19</v>
-      </c>
-      <c r="H32" s="16" t="n">
-        <v>9.59</v>
-      </c>
-      <c r="I32" s="15" t="n">
-        <v>14.59</v>
+        <v>17.52</v>
+      </c>
+      <c r="H32" s="15" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="I32" s="17" t="n">
+        <v>10.59</v>
       </c>
       <c r="J32" s="15" t="n">
-        <v>18.11</v>
-      </c>
-      <c r="K32" s="15" t="n">
-        <v>13.64</v>
-      </c>
-      <c r="M32" s="17" t="n">
-        <v>13.62</v>
+        <v>14.77</v>
+      </c>
+      <c r="K32" s="17" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="M32" s="16" t="n">
+        <v>14.45</v>
       </c>
       <c r="N32" s="14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O32" s="15" t="n">
-        <v>14.51</v>
-      </c>
-      <c r="P32" s="16" t="n">
-        <v>9.42</v>
+        <v>14.12</v>
+      </c>
+      <c r="P32" s="17" t="n">
+        <v>10.48</v>
       </c>
       <c r="Q32" s="15" t="n">
-        <v>13.28</v>
+        <v>13.9</v>
       </c>
       <c r="R32" s="15" t="n">
-        <v>13.6</v>
+        <v>16.58</v>
       </c>
       <c r="S32" s="15" t="n">
-        <v>12.31</v>
+        <v>14.24</v>
       </c>
       <c r="T32" s="15" t="n">
-        <v>14.28</v>
+        <v>12.56</v>
       </c>
       <c r="U32" s="15" t="n">
-        <v>17.68</v>
-      </c>
-      <c r="V32" s="16" t="n">
-        <v>9.279999999999999</v>
-      </c>
-      <c r="W32" s="17" t="n">
-        <v>12.7</v>
+        <v>14.98</v>
+      </c>
+      <c r="V32" s="15" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="W32" s="16" t="n">
+        <v>14.03</v>
       </c>
       <c r="X32" s="18" t="n">
-        <v>13.16</v>
+        <v>14.24</v>
       </c>
       <c r="Y32" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z32" s="21" t="inlineStr">
+      <c r="Z32" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -6543,83 +6814,83 @@
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="13" t="inlineStr">
         <is>
-          <t>N915546</t>
+          <t>F608380</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>Ettahiri</t>
+          <t>Derfoufi</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr">
         <is>
-          <t>Loubna</t>
+          <t>Khalid</t>
         </is>
       </c>
       <c r="D33" s="14" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E33" s="15" t="n">
-        <v>14.12</v>
+        <v>13.47</v>
       </c>
       <c r="F33" s="15" t="n">
-        <v>13.35</v>
-      </c>
-      <c r="G33" s="16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="H33" s="15" t="n">
-        <v>19.42</v>
+        <v>12.92</v>
+      </c>
+      <c r="G33" s="15" t="n">
+        <v>14.19</v>
+      </c>
+      <c r="H33" s="17" t="n">
+        <v>9.59</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>12.01</v>
+        <v>14.59</v>
       </c>
       <c r="J33" s="15" t="n">
-        <v>13.22</v>
+        <v>18.11</v>
       </c>
       <c r="K33" s="15" t="n">
-        <v>15.32</v>
-      </c>
-      <c r="M33" s="17" t="n">
-        <v>13.83</v>
+        <v>13.64</v>
+      </c>
+      <c r="M33" s="16" t="n">
+        <v>13.62</v>
       </c>
       <c r="N33" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O33" s="15" t="n">
-        <v>17.58</v>
-      </c>
-      <c r="P33" s="15" t="n">
-        <v>16.14</v>
-      </c>
-      <c r="Q33" s="16" t="n">
-        <v>8.99</v>
+        <v>14.51</v>
+      </c>
+      <c r="P33" s="17" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="Q33" s="15" t="n">
+        <v>13.28</v>
       </c>
       <c r="R33" s="15" t="n">
-        <v>17.15</v>
+        <v>13.6</v>
       </c>
       <c r="S33" s="15" t="n">
-        <v>16.18</v>
+        <v>12.31</v>
       </c>
       <c r="T33" s="15" t="n">
-        <v>18.16</v>
+        <v>14.28</v>
       </c>
       <c r="U33" s="15" t="n">
-        <v>18.61</v>
-      </c>
-      <c r="V33" s="16" t="n">
-        <v>10.76</v>
-      </c>
-      <c r="W33" s="17" t="n">
-        <v>15.03</v>
+        <v>17.68</v>
+      </c>
+      <c r="V33" s="17" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="W33" s="16" t="n">
+        <v>12.7</v>
       </c>
       <c r="X33" s="18" t="n">
-        <v>14.43</v>
+        <v>13.16</v>
       </c>
       <c r="Y33" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z33" s="21" t="inlineStr">
+      <c r="Z33" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -6628,83 +6899,83 @@
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>H718051</t>
+          <t>N915546</t>
         </is>
       </c>
       <c r="B34" s="20" t="inlineStr">
         <is>
-          <t>Faqir</t>
+          <t>Elouafi</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
         <is>
-          <t>Anas</t>
+          <t>Loubna</t>
         </is>
       </c>
       <c r="D34" s="14" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E34" s="15" t="n">
-        <v>17.77</v>
+        <v>14.12</v>
       </c>
       <c r="F34" s="15" t="n">
-        <v>14.44</v>
-      </c>
-      <c r="G34" s="15" t="n">
-        <v>14.45</v>
+        <v>13.35</v>
+      </c>
+      <c r="G34" s="17" t="n">
+        <v>10.5</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>16.61</v>
+        <v>19.42</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="J34" s="16" t="n">
-        <v>9.51</v>
+        <v>12.01</v>
+      </c>
+      <c r="J34" s="15" t="n">
+        <v>13.22</v>
       </c>
       <c r="K34" s="15" t="n">
-        <v>13.96</v>
-      </c>
-      <c r="M34" s="17" t="n">
-        <v>15</v>
+        <v>15.32</v>
+      </c>
+      <c r="M34" s="16" t="n">
+        <v>13.83</v>
       </c>
       <c r="N34" s="14" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="O34" s="15" t="n">
-        <v>14.28</v>
+        <v>17.58</v>
       </c>
       <c r="P34" s="15" t="n">
-        <v>13.53</v>
-      </c>
-      <c r="Q34" s="15" t="n">
-        <v>16.98</v>
-      </c>
-      <c r="R34" s="16" t="n">
-        <v>11.77</v>
+        <v>16.14</v>
+      </c>
+      <c r="Q34" s="17" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="R34" s="15" t="n">
+        <v>17.15</v>
       </c>
       <c r="S34" s="15" t="n">
-        <v>15.41</v>
+        <v>16.18</v>
       </c>
       <c r="T34" s="15" t="n">
-        <v>14.11</v>
-      </c>
-      <c r="U34" s="16" t="n">
-        <v>10.89</v>
-      </c>
-      <c r="V34" s="15" t="n">
-        <v>12.15</v>
-      </c>
-      <c r="W34" s="17" t="n">
-        <v>13.78</v>
+        <v>18.16</v>
+      </c>
+      <c r="U34" s="15" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="V34" s="17" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="W34" s="16" t="n">
+        <v>15.03</v>
       </c>
       <c r="X34" s="18" t="n">
-        <v>14.39</v>
+        <v>14.43</v>
       </c>
       <c r="Y34" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z34" s="21" t="inlineStr">
+      <c r="Z34" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -6713,83 +6984,83 @@
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>T572193</t>
+          <t>H718051</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>Grari</t>
+          <t>Fekhari</t>
         </is>
       </c>
       <c r="C35" s="13" t="inlineStr">
         <is>
-          <t>Zineb</t>
+          <t>Anas</t>
         </is>
       </c>
       <c r="D35" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="E35" s="16" t="n">
-        <v>10.6</v>
+        <v>19</v>
+      </c>
+      <c r="E35" s="15" t="n">
+        <v>17.77</v>
       </c>
       <c r="F35" s="15" t="n">
-        <v>12.43</v>
+        <v>14.44</v>
       </c>
       <c r="G35" s="15" t="n">
-        <v>16.33</v>
+        <v>14.45</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>18.73</v>
+        <v>16.61</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>17.48</v>
-      </c>
-      <c r="J35" s="15" t="n">
-        <v>12.81</v>
+        <v>16.2</v>
+      </c>
+      <c r="J35" s="17" t="n">
+        <v>9.51</v>
       </c>
       <c r="K35" s="15" t="n">
-        <v>16.51</v>
-      </c>
-      <c r="M35" s="17" t="n">
-        <v>14.81</v>
+        <v>13.96</v>
+      </c>
+      <c r="M35" s="16" t="n">
+        <v>15</v>
       </c>
       <c r="N35" s="14" t="n">
-        <v>10</v>
-      </c>
-      <c r="O35" s="16" t="n">
-        <v>10.84</v>
-      </c>
-      <c r="P35" s="16" t="n">
-        <v>10.71</v>
+        <v>17</v>
+      </c>
+      <c r="O35" s="15" t="n">
+        <v>14.28</v>
+      </c>
+      <c r="P35" s="15" t="n">
+        <v>13.53</v>
       </c>
       <c r="Q35" s="15" t="n">
-        <v>13.74</v>
-      </c>
-      <c r="R35" s="15" t="n">
-        <v>14.55</v>
+        <v>16.98</v>
+      </c>
+      <c r="R35" s="17" t="n">
+        <v>11.77</v>
       </c>
       <c r="S35" s="15" t="n">
-        <v>16.23</v>
+        <v>15.41</v>
       </c>
       <c r="T35" s="15" t="n">
-        <v>15.48</v>
-      </c>
-      <c r="U35" s="15" t="n">
-        <v>13.85</v>
+        <v>14.11</v>
+      </c>
+      <c r="U35" s="17" t="n">
+        <v>10.89</v>
       </c>
       <c r="V35" s="15" t="n">
-        <v>18.69</v>
-      </c>
-      <c r="W35" s="17" t="n">
-        <v>14.15</v>
+        <v>12.15</v>
+      </c>
+      <c r="W35" s="16" t="n">
+        <v>13.78</v>
       </c>
       <c r="X35" s="18" t="n">
-        <v>14.48</v>
+        <v>14.39</v>
       </c>
       <c r="Y35" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z35" s="21" t="inlineStr">
+      <c r="Z35" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -6798,83 +7069,83 @@
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>G223327</t>
+          <t>T572193</t>
         </is>
       </c>
       <c r="B36" s="20" t="inlineStr">
         <is>
-          <t>Hannioui</t>
+          <t>Guennouni</t>
         </is>
       </c>
       <c r="C36" s="20" t="inlineStr">
         <is>
-          <t>Reda</t>
+          <t>Zineb</t>
         </is>
       </c>
       <c r="D36" s="14" t="n">
-        <v>19</v>
-      </c>
-      <c r="E36" s="16" t="n">
-        <v>9.1</v>
+        <v>2</v>
+      </c>
+      <c r="E36" s="17" t="n">
+        <v>10.6</v>
       </c>
       <c r="F36" s="15" t="n">
-        <v>16.82</v>
+        <v>12.43</v>
       </c>
       <c r="G36" s="15" t="n">
-        <v>14.98</v>
+        <v>16.33</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>12.56</v>
+        <v>18.73</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>17.43</v>
+        <v>17.48</v>
       </c>
       <c r="J36" s="15" t="n">
-        <v>15.17</v>
+        <v>12.81</v>
       </c>
       <c r="K36" s="15" t="n">
-        <v>13.73</v>
-      </c>
-      <c r="M36" s="17" t="n">
-        <v>14.18</v>
+        <v>16.51</v>
+      </c>
+      <c r="M36" s="16" t="n">
+        <v>14.81</v>
       </c>
       <c r="N36" s="14" t="n">
-        <v>12</v>
-      </c>
-      <c r="O36" s="16" t="n">
-        <v>8.890000000000001</v>
-      </c>
-      <c r="P36" s="15" t="n">
-        <v>13.29</v>
+        <v>10</v>
+      </c>
+      <c r="O36" s="17" t="n">
+        <v>10.84</v>
+      </c>
+      <c r="P36" s="17" t="n">
+        <v>10.71</v>
       </c>
       <c r="Q36" s="15" t="n">
-        <v>19.09</v>
+        <v>13.74</v>
       </c>
       <c r="R36" s="15" t="n">
-        <v>15.35</v>
+        <v>14.55</v>
       </c>
       <c r="S36" s="15" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="T36" s="16" t="n">
-        <v>11.65</v>
+        <v>16.23</v>
+      </c>
+      <c r="T36" s="15" t="n">
+        <v>15.48</v>
       </c>
       <c r="U36" s="15" t="n">
-        <v>18.4</v>
+        <v>13.85</v>
       </c>
       <c r="V36" s="15" t="n">
-        <v>14.55</v>
-      </c>
-      <c r="W36" s="17" t="n">
-        <v>14.51</v>
+        <v>18.69</v>
+      </c>
+      <c r="W36" s="16" t="n">
+        <v>14.15</v>
       </c>
       <c r="X36" s="18" t="n">
-        <v>14.34</v>
+        <v>14.48</v>
       </c>
       <c r="Y36" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z36" s="21" t="inlineStr">
+      <c r="Z36" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -6883,83 +7154,83 @@
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="13" t="inlineStr">
         <is>
-          <t>N900081</t>
+          <t>G223327</t>
         </is>
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>Ibourk</t>
+          <t>Hajouji</t>
         </is>
       </c>
       <c r="C37" s="13" t="inlineStr">
         <is>
-          <t>Meryem</t>
+          <t>Reda</t>
         </is>
       </c>
       <c r="D37" s="14" t="n">
-        <v>15</v>
-      </c>
-      <c r="E37" s="15" t="n">
-        <v>12.87</v>
-      </c>
-      <c r="F37" s="16" t="n">
-        <v>11.67</v>
+        <v>19</v>
+      </c>
+      <c r="E37" s="17" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="F37" s="15" t="n">
+        <v>16.82</v>
       </c>
       <c r="G37" s="15" t="n">
-        <v>13</v>
+        <v>14.98</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>12.28</v>
+        <v>12.56</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>18.94</v>
-      </c>
-      <c r="J37" s="16" t="n">
-        <v>10.81</v>
+        <v>17.43</v>
+      </c>
+      <c r="J37" s="15" t="n">
+        <v>15.17</v>
       </c>
       <c r="K37" s="15" t="n">
-        <v>13.98</v>
-      </c>
-      <c r="M37" s="17" t="n">
-        <v>13.34</v>
+        <v>13.73</v>
+      </c>
+      <c r="M37" s="16" t="n">
+        <v>14.18</v>
       </c>
       <c r="N37" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="O37" s="15" t="n">
-        <v>12.3</v>
+        <v>12</v>
+      </c>
+      <c r="O37" s="17" t="n">
+        <v>8.890000000000001</v>
       </c>
       <c r="P37" s="15" t="n">
-        <v>17.46</v>
+        <v>13.29</v>
       </c>
       <c r="Q37" s="15" t="n">
-        <v>15.12</v>
-      </c>
-      <c r="R37" s="16" t="n">
-        <v>10.89</v>
+        <v>19.09</v>
+      </c>
+      <c r="R37" s="15" t="n">
+        <v>15.35</v>
       </c>
       <c r="S37" s="15" t="n">
-        <v>14.25</v>
-      </c>
-      <c r="T37" s="15" t="n">
-        <v>15.69</v>
+        <v>15.7</v>
+      </c>
+      <c r="T37" s="17" t="n">
+        <v>11.65</v>
       </c>
       <c r="U37" s="15" t="n">
-        <v>16.94</v>
+        <v>18.4</v>
       </c>
       <c r="V37" s="15" t="n">
-        <v>17.89</v>
-      </c>
-      <c r="W37" s="17" t="n">
-        <v>15.07</v>
+        <v>14.55</v>
+      </c>
+      <c r="W37" s="16" t="n">
+        <v>14.51</v>
       </c>
       <c r="X37" s="18" t="n">
-        <v>14.21</v>
+        <v>14.34</v>
       </c>
       <c r="Y37" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z37" s="21" t="inlineStr">
+      <c r="Z37" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
@@ -6968,88 +7239,89 @@
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>G783247</t>
+          <t>N900081</t>
         </is>
       </c>
       <c r="B38" s="20" t="inlineStr">
         <is>
-          <t>Jabrane</t>
+          <t>Ikken</t>
         </is>
       </c>
       <c r="C38" s="20" t="inlineStr">
         <is>
-          <t>Nabil</t>
+          <t>Meryem</t>
         </is>
       </c>
       <c r="D38" s="14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E38" s="15" t="n">
-        <v>15.11</v>
-      </c>
-      <c r="F38" s="15" t="n">
-        <v>15.49</v>
+        <v>12.87</v>
+      </c>
+      <c r="F38" s="17" t="n">
+        <v>11.67</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>15.91</v>
+        <v>13</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>15.01</v>
+        <v>12.28</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>15.62</v>
-      </c>
-      <c r="J38" s="16" t="n">
-        <v>9.81</v>
-      </c>
-      <c r="K38" s="16" t="n">
-        <v>9.619999999999999</v>
-      </c>
-      <c r="M38" s="17" t="n">
+        <v>18.94</v>
+      </c>
+      <c r="J38" s="17" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="K38" s="15" t="n">
+        <v>13.98</v>
+      </c>
+      <c r="M38" s="16" t="n">
+        <v>13.34</v>
+      </c>
+      <c r="N38" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="O38" s="15" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="P38" s="15" t="n">
+        <v>17.46</v>
+      </c>
+      <c r="Q38" s="15" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="R38" s="17" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="S38" s="15" t="n">
         <v>14.25</v>
       </c>
-      <c r="N38" s="14" t="n">
-        <v>15</v>
-      </c>
-      <c r="O38" s="15" t="n">
-        <v>12.48</v>
-      </c>
-      <c r="P38" s="15" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="Q38" s="15" t="n">
-        <v>15.39</v>
-      </c>
-      <c r="R38" s="16" t="n">
-        <v>7.86</v>
-      </c>
-      <c r="S38" s="15" t="n">
-        <v>14.1</v>
-      </c>
       <c r="T38" s="15" t="n">
-        <v>16.58</v>
+        <v>15.69</v>
       </c>
       <c r="U38" s="15" t="n">
-        <v>18.94</v>
+        <v>16.94</v>
       </c>
       <c r="V38" s="15" t="n">
-        <v>14.84</v>
-      </c>
-      <c r="W38" s="17" t="n">
-        <v>13.9</v>
+        <v>17.89</v>
+      </c>
+      <c r="W38" s="16" t="n">
+        <v>15.07</v>
       </c>
       <c r="X38" s="18" t="n">
-        <v>14.07</v>
+        <v>14.21</v>
       </c>
       <c r="Y38" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Z38" s="21" t="inlineStr">
+      <c r="Z38" s="19" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
     </row>
+    <row r="39"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="N2:W2"/>
@@ -7060,4 +7332,1155 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="3" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>DÉPARTEMENT GEE GÉNIE ÉLECTRIQUE ET ÉLECTRONIQUE — TROISIÈME ANNÉE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>Informations Générales</t>
+        </is>
+      </c>
+      <c r="D2" s="25" t="inlineStr">
+        <is>
+          <t>SEMESTRE 5</t>
+        </is>
+      </c>
+      <c r="N2" s="25" t="inlineStr">
+        <is>
+          <t>SEMESTRE 6</t>
+        </is>
+      </c>
+      <c r="O2" s="25" t="n"/>
+      <c r="P2" s="25" t="n"/>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="3" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Coef 5</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Coef 5</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Coef 5</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Coef 4</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>Coef 4</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>Coef 3</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>Coef 3</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="33" t="inlineStr">
+        <is>
+          <t>Coef 20</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="n"/>
+      <c r="P3" s="4" t="n"/>
+    </row>
+    <row r="4" ht="54" customHeight="1">
+      <c r="A4" s="26" t="inlineStr">
+        <is>
+          <t>CNE</t>
+        </is>
+      </c>
+      <c r="B4" s="26" t="inlineStr">
+        <is>
+          <t>Nom</t>
+        </is>
+      </c>
+      <c r="C4" s="26" t="inlineStr">
+        <is>
+          <t>Prénom</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="inlineStr">
+        <is>
+          <t>Absences S5</t>
+        </is>
+      </c>
+      <c r="E4" s="27" t="inlineStr">
+        <is>
+          <t>Électronique de Puissance Avancée</t>
+        </is>
+      </c>
+      <c r="F4" s="27" t="inlineStr">
+        <is>
+          <t>Commande Numérique</t>
+        </is>
+      </c>
+      <c r="G4" s="27" t="inlineStr">
+        <is>
+          <t>Mathématiques 5</t>
+        </is>
+      </c>
+      <c r="H4" s="27" t="inlineStr">
+        <is>
+          <t>Systèmes de Stockage d'Énergie</t>
+        </is>
+      </c>
+      <c r="I4" s="27" t="inlineStr">
+        <is>
+          <t>Smart Grid</t>
+        </is>
+      </c>
+      <c r="J4" s="27" t="inlineStr">
+        <is>
+          <t>Anglais Professionnel</t>
+        </is>
+      </c>
+      <c r="K4" s="27" t="inlineStr">
+        <is>
+          <t>Français Professionnel 5</t>
+        </is>
+      </c>
+      <c r="M4" s="7" t="inlineStr">
+        <is>
+          <t>Moyenne
+SEMESTRE 5</t>
+        </is>
+      </c>
+      <c r="N4" s="34" t="inlineStr">
+        <is>
+          <t>PFE</t>
+        </is>
+      </c>
+      <c r="O4" s="10" t="inlineStr">
+        <is>
+          <t>Moyenne
+Annuelle
+3ème Année</t>
+        </is>
+      </c>
+      <c r="P4" s="12" t="inlineStr">
+        <is>
+          <t>Redoublant</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>H358033</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Chrif</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Omar</t>
+        </is>
+      </c>
+      <c r="D5" s="35" t="n"/>
+      <c r="E5" s="29" t="n"/>
+      <c r="F5" s="29" t="n"/>
+      <c r="G5" s="29" t="n"/>
+      <c r="H5" s="29" t="n"/>
+      <c r="I5" s="29" t="n"/>
+      <c r="J5" s="29" t="n"/>
+      <c r="K5" s="29" t="n"/>
+      <c r="L5" s="36" t="n"/>
+      <c r="M5" s="16" t="n"/>
+      <c r="N5" s="37" t="n"/>
+      <c r="O5" s="38" t="n"/>
+      <c r="P5" s="31" t="n"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="39" t="inlineStr">
+        <is>
+          <t>R973043</t>
+        </is>
+      </c>
+      <c r="B6" s="39" t="inlineStr">
+        <is>
+          <t>Dahak</t>
+        </is>
+      </c>
+      <c r="C6" s="39" t="inlineStr">
+        <is>
+          <t>Samira</t>
+        </is>
+      </c>
+      <c r="D6" s="35" t="n"/>
+      <c r="E6" s="29" t="n"/>
+      <c r="F6" s="29" t="n"/>
+      <c r="G6" s="29" t="n"/>
+      <c r="H6" s="29" t="n"/>
+      <c r="I6" s="29" t="n"/>
+      <c r="J6" s="29" t="n"/>
+      <c r="K6" s="29" t="n"/>
+      <c r="L6" s="36" t="n"/>
+      <c r="M6" s="16" t="n"/>
+      <c r="N6" s="37" t="n"/>
+      <c r="O6" s="38" t="n"/>
+      <c r="P6" s="31" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>N368265</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>El Boukili</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Karim</t>
+        </is>
+      </c>
+      <c r="D7" s="35" t="n"/>
+      <c r="E7" s="29" t="n"/>
+      <c r="F7" s="29" t="n"/>
+      <c r="G7" s="29" t="n"/>
+      <c r="H7" s="29" t="n"/>
+      <c r="I7" s="29" t="n"/>
+      <c r="J7" s="29" t="n"/>
+      <c r="K7" s="29" t="n"/>
+      <c r="L7" s="36" t="n"/>
+      <c r="M7" s="16" t="n"/>
+      <c r="N7" s="37" t="n"/>
+      <c r="O7" s="38" t="n"/>
+      <c r="P7" s="31" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="39" t="inlineStr">
+        <is>
+          <t>M674923</t>
+        </is>
+      </c>
+      <c r="B8" s="39" t="inlineStr">
+        <is>
+          <t>Fahr</t>
+        </is>
+      </c>
+      <c r="C8" s="39" t="inlineStr">
+        <is>
+          <t>Rim</t>
+        </is>
+      </c>
+      <c r="D8" s="35" t="n"/>
+      <c r="E8" s="29" t="n"/>
+      <c r="F8" s="29" t="n"/>
+      <c r="G8" s="29" t="n"/>
+      <c r="H8" s="29" t="n"/>
+      <c r="I8" s="29" t="n"/>
+      <c r="J8" s="29" t="n"/>
+      <c r="K8" s="29" t="n"/>
+      <c r="L8" s="36" t="n"/>
+      <c r="M8" s="16" t="n"/>
+      <c r="N8" s="37" t="n"/>
+      <c r="O8" s="38" t="n"/>
+      <c r="P8" s="31" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>G867003</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>Ghazali</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Amine</t>
+        </is>
+      </c>
+      <c r="D9" s="35" t="n"/>
+      <c r="E9" s="29" t="n"/>
+      <c r="F9" s="29" t="n"/>
+      <c r="G9" s="29" t="n"/>
+      <c r="H9" s="29" t="n"/>
+      <c r="I9" s="29" t="n"/>
+      <c r="J9" s="29" t="n"/>
+      <c r="K9" s="29" t="n"/>
+      <c r="L9" s="36" t="n"/>
+      <c r="M9" s="16" t="n"/>
+      <c r="N9" s="37" t="n"/>
+      <c r="O9" s="38" t="n"/>
+      <c r="P9" s="31" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="39" t="inlineStr">
+        <is>
+          <t>N648936</t>
+        </is>
+      </c>
+      <c r="B10" s="39" t="inlineStr">
+        <is>
+          <t>Hachimi</t>
+        </is>
+      </c>
+      <c r="C10" s="39" t="inlineStr">
+        <is>
+          <t>Latifa</t>
+        </is>
+      </c>
+      <c r="D10" s="35" t="n"/>
+      <c r="E10" s="29" t="n"/>
+      <c r="F10" s="29" t="n"/>
+      <c r="G10" s="29" t="n"/>
+      <c r="H10" s="29" t="n"/>
+      <c r="I10" s="29" t="n"/>
+      <c r="J10" s="29" t="n"/>
+      <c r="K10" s="29" t="n"/>
+      <c r="L10" s="36" t="n"/>
+      <c r="M10" s="16" t="n"/>
+      <c r="N10" s="37" t="n"/>
+      <c r="O10" s="38" t="n"/>
+      <c r="P10" s="31" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>T714533</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Idali</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Tarik</t>
+        </is>
+      </c>
+      <c r="D11" s="35" t="n"/>
+      <c r="E11" s="29" t="n"/>
+      <c r="F11" s="29" t="n"/>
+      <c r="G11" s="29" t="n"/>
+      <c r="H11" s="29" t="n"/>
+      <c r="I11" s="29" t="n"/>
+      <c r="J11" s="29" t="n"/>
+      <c r="K11" s="29" t="n"/>
+      <c r="L11" s="36" t="n"/>
+      <c r="M11" s="16" t="n"/>
+      <c r="N11" s="37" t="n"/>
+      <c r="O11" s="38" t="n"/>
+      <c r="P11" s="31" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="39" t="inlineStr">
+        <is>
+          <t>T505557</t>
+        </is>
+      </c>
+      <c r="B12" s="39" t="inlineStr">
+        <is>
+          <t>Jalili</t>
+        </is>
+      </c>
+      <c r="C12" s="39" t="inlineStr">
+        <is>
+          <t>Houda</t>
+        </is>
+      </c>
+      <c r="D12" s="35" t="n"/>
+      <c r="E12" s="29" t="n"/>
+      <c r="F12" s="29" t="n"/>
+      <c r="G12" s="29" t="n"/>
+      <c r="H12" s="29" t="n"/>
+      <c r="I12" s="29" t="n"/>
+      <c r="J12" s="29" t="n"/>
+      <c r="K12" s="29" t="n"/>
+      <c r="L12" s="36" t="n"/>
+      <c r="M12" s="16" t="n"/>
+      <c r="N12" s="37" t="n"/>
+      <c r="O12" s="38" t="n"/>
+      <c r="P12" s="31" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>B523513</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>Kaabi</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>Bilal</t>
+        </is>
+      </c>
+      <c r="D13" s="35" t="n"/>
+      <c r="E13" s="29" t="n"/>
+      <c r="F13" s="29" t="n"/>
+      <c r="G13" s="29" t="n"/>
+      <c r="H13" s="29" t="n"/>
+      <c r="I13" s="29" t="n"/>
+      <c r="J13" s="29" t="n"/>
+      <c r="K13" s="29" t="n"/>
+      <c r="L13" s="36" t="n"/>
+      <c r="M13" s="16" t="n"/>
+      <c r="N13" s="37" t="n"/>
+      <c r="O13" s="38" t="n"/>
+      <c r="P13" s="31" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="39" t="inlineStr">
+        <is>
+          <t>K993987</t>
+        </is>
+      </c>
+      <c r="B14" s="39" t="inlineStr">
+        <is>
+          <t>Lagrini</t>
+        </is>
+      </c>
+      <c r="C14" s="39" t="inlineStr">
+        <is>
+          <t>Sara</t>
+        </is>
+      </c>
+      <c r="D14" s="35" t="n"/>
+      <c r="E14" s="29" t="n"/>
+      <c r="F14" s="29" t="n"/>
+      <c r="G14" s="29" t="n"/>
+      <c r="H14" s="29" t="n"/>
+      <c r="I14" s="29" t="n"/>
+      <c r="J14" s="29" t="n"/>
+      <c r="K14" s="29" t="n"/>
+      <c r="L14" s="36" t="n"/>
+      <c r="M14" s="16" t="n"/>
+      <c r="N14" s="37" t="n"/>
+      <c r="O14" s="38" t="n"/>
+      <c r="P14" s="31" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>F129721</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>Mhammedi</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>Mehdi</t>
+        </is>
+      </c>
+      <c r="D15" s="35" t="n"/>
+      <c r="E15" s="29" t="n"/>
+      <c r="F15" s="29" t="n"/>
+      <c r="G15" s="29" t="n"/>
+      <c r="H15" s="29" t="n"/>
+      <c r="I15" s="29" t="n"/>
+      <c r="J15" s="29" t="n"/>
+      <c r="K15" s="29" t="n"/>
+      <c r="L15" s="36" t="n"/>
+      <c r="M15" s="16" t="n"/>
+      <c r="N15" s="37" t="n"/>
+      <c r="O15" s="38" t="n"/>
+      <c r="P15" s="31" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="39" t="inlineStr">
+        <is>
+          <t>N370744</t>
+        </is>
+      </c>
+      <c r="B16" s="39" t="inlineStr">
+        <is>
+          <t>Nassiri</t>
+        </is>
+      </c>
+      <c r="C16" s="39" t="inlineStr">
+        <is>
+          <t>Ghita</t>
+        </is>
+      </c>
+      <c r="D16" s="35" t="n"/>
+      <c r="E16" s="29" t="n"/>
+      <c r="F16" s="29" t="n"/>
+      <c r="G16" s="29" t="n"/>
+      <c r="H16" s="29" t="n"/>
+      <c r="I16" s="29" t="n"/>
+      <c r="J16" s="29" t="n"/>
+      <c r="K16" s="29" t="n"/>
+      <c r="L16" s="36" t="n"/>
+      <c r="M16" s="16" t="n"/>
+      <c r="N16" s="37" t="n"/>
+      <c r="O16" s="38" t="n"/>
+      <c r="P16" s="31" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>K600971</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>Ouad</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>Ayoub</t>
+        </is>
+      </c>
+      <c r="D17" s="35" t="n"/>
+      <c r="E17" s="29" t="n"/>
+      <c r="F17" s="29" t="n"/>
+      <c r="G17" s="29" t="n"/>
+      <c r="H17" s="29" t="n"/>
+      <c r="I17" s="29" t="n"/>
+      <c r="J17" s="29" t="n"/>
+      <c r="K17" s="29" t="n"/>
+      <c r="L17" s="36" t="n"/>
+      <c r="M17" s="16" t="n"/>
+      <c r="N17" s="37" t="n"/>
+      <c r="O17" s="38" t="n"/>
+      <c r="P17" s="31" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="39" t="inlineStr">
+        <is>
+          <t>H464143</t>
+        </is>
+      </c>
+      <c r="B18" s="39" t="inlineStr">
+        <is>
+          <t>Qaissi</t>
+        </is>
+      </c>
+      <c r="C18" s="39" t="inlineStr">
+        <is>
+          <t>Hafsa</t>
+        </is>
+      </c>
+      <c r="D18" s="35" t="n"/>
+      <c r="E18" s="29" t="n"/>
+      <c r="F18" s="29" t="n"/>
+      <c r="G18" s="29" t="n"/>
+      <c r="H18" s="29" t="n"/>
+      <c r="I18" s="29" t="n"/>
+      <c r="J18" s="29" t="n"/>
+      <c r="K18" s="29" t="n"/>
+      <c r="L18" s="36" t="n"/>
+      <c r="M18" s="16" t="n"/>
+      <c r="N18" s="37" t="n"/>
+      <c r="O18" s="38" t="n"/>
+      <c r="P18" s="31" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>P414245</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>Regragui</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>Adil</t>
+        </is>
+      </c>
+      <c r="D19" s="35" t="n"/>
+      <c r="E19" s="29" t="n"/>
+      <c r="F19" s="29" t="n"/>
+      <c r="G19" s="29" t="n"/>
+      <c r="H19" s="29" t="n"/>
+      <c r="I19" s="29" t="n"/>
+      <c r="J19" s="29" t="n"/>
+      <c r="K19" s="29" t="n"/>
+      <c r="L19" s="36" t="n"/>
+      <c r="M19" s="16" t="n"/>
+      <c r="N19" s="37" t="n"/>
+      <c r="O19" s="38" t="n"/>
+      <c r="P19" s="31" t="n"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="39" t="inlineStr">
+        <is>
+          <t>T570857</t>
+        </is>
+      </c>
+      <c r="B20" s="39" t="inlineStr">
+        <is>
+          <t>Sekkat</t>
+        </is>
+      </c>
+      <c r="C20" s="39" t="inlineStr">
+        <is>
+          <t>Meriem</t>
+        </is>
+      </c>
+      <c r="D20" s="35" t="n"/>
+      <c r="E20" s="29" t="n"/>
+      <c r="F20" s="29" t="n"/>
+      <c r="G20" s="29" t="n"/>
+      <c r="H20" s="29" t="n"/>
+      <c r="I20" s="29" t="n"/>
+      <c r="J20" s="29" t="n"/>
+      <c r="K20" s="29" t="n"/>
+      <c r="L20" s="36" t="n"/>
+      <c r="M20" s="16" t="n"/>
+      <c r="N20" s="37" t="n"/>
+      <c r="O20" s="38" t="n"/>
+      <c r="P20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>R901405</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>Tahri</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>Driss</t>
+        </is>
+      </c>
+      <c r="D21" s="35" t="n"/>
+      <c r="E21" s="29" t="n"/>
+      <c r="F21" s="29" t="n"/>
+      <c r="G21" s="29" t="n"/>
+      <c r="H21" s="29" t="n"/>
+      <c r="I21" s="29" t="n"/>
+      <c r="J21" s="29" t="n"/>
+      <c r="K21" s="29" t="n"/>
+      <c r="L21" s="36" t="n"/>
+      <c r="M21" s="16" t="n"/>
+      <c r="N21" s="37" t="n"/>
+      <c r="O21" s="38" t="n"/>
+      <c r="P21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="39" t="inlineStr">
+        <is>
+          <t>K559446</t>
+        </is>
+      </c>
+      <c r="B22" s="39" t="inlineStr">
+        <is>
+          <t>Ufkir</t>
+        </is>
+      </c>
+      <c r="C22" s="39" t="inlineStr">
+        <is>
+          <t>Widad</t>
+        </is>
+      </c>
+      <c r="D22" s="35" t="n"/>
+      <c r="E22" s="29" t="n"/>
+      <c r="F22" s="29" t="n"/>
+      <c r="G22" s="29" t="n"/>
+      <c r="H22" s="29" t="n"/>
+      <c r="I22" s="29" t="n"/>
+      <c r="J22" s="29" t="n"/>
+      <c r="K22" s="29" t="n"/>
+      <c r="L22" s="36" t="n"/>
+      <c r="M22" s="16" t="n"/>
+      <c r="N22" s="37" t="n"/>
+      <c r="O22" s="38" t="n"/>
+      <c r="P22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>H592958</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>Vantomme</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>Hamza</t>
+        </is>
+      </c>
+      <c r="D23" s="35" t="n"/>
+      <c r="E23" s="29" t="n"/>
+      <c r="F23" s="29" t="n"/>
+      <c r="G23" s="29" t="n"/>
+      <c r="H23" s="29" t="n"/>
+      <c r="I23" s="29" t="n"/>
+      <c r="J23" s="29" t="n"/>
+      <c r="K23" s="29" t="n"/>
+      <c r="L23" s="36" t="n"/>
+      <c r="M23" s="16" t="n"/>
+      <c r="N23" s="37" t="n"/>
+      <c r="O23" s="38" t="n"/>
+      <c r="P23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="39" t="inlineStr">
+        <is>
+          <t>K163546</t>
+        </is>
+      </c>
+      <c r="B24" s="39" t="inlineStr">
+        <is>
+          <t>Wardi</t>
+        </is>
+      </c>
+      <c r="C24" s="39" t="inlineStr">
+        <is>
+          <t>Chaimaa</t>
+        </is>
+      </c>
+      <c r="D24" s="35" t="n"/>
+      <c r="E24" s="29" t="n"/>
+      <c r="F24" s="29" t="n"/>
+      <c r="G24" s="29" t="n"/>
+      <c r="H24" s="29" t="n"/>
+      <c r="I24" s="29" t="n"/>
+      <c r="J24" s="29" t="n"/>
+      <c r="K24" s="29" t="n"/>
+      <c r="L24" s="36" t="n"/>
+      <c r="M24" s="16" t="n"/>
+      <c r="N24" s="37" t="n"/>
+      <c r="O24" s="38" t="n"/>
+      <c r="P24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>F964255</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>Xarfi</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>Zakaria</t>
+        </is>
+      </c>
+      <c r="D25" s="35" t="n"/>
+      <c r="E25" s="29" t="n"/>
+      <c r="F25" s="29" t="n"/>
+      <c r="G25" s="29" t="n"/>
+      <c r="H25" s="29" t="n"/>
+      <c r="I25" s="29" t="n"/>
+      <c r="J25" s="29" t="n"/>
+      <c r="K25" s="29" t="n"/>
+      <c r="L25" s="36" t="n"/>
+      <c r="M25" s="16" t="n"/>
+      <c r="N25" s="37" t="n"/>
+      <c r="O25" s="38" t="n"/>
+      <c r="P25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="39" t="inlineStr">
+        <is>
+          <t>P212869</t>
+        </is>
+      </c>
+      <c r="B26" s="39" t="inlineStr">
+        <is>
+          <t>Yatribi</t>
+        </is>
+      </c>
+      <c r="C26" s="39" t="inlineStr">
+        <is>
+          <t>Fatima</t>
+        </is>
+      </c>
+      <c r="D26" s="35" t="n"/>
+      <c r="E26" s="29" t="n"/>
+      <c r="F26" s="29" t="n"/>
+      <c r="G26" s="29" t="n"/>
+      <c r="H26" s="29" t="n"/>
+      <c r="I26" s="29" t="n"/>
+      <c r="J26" s="29" t="n"/>
+      <c r="K26" s="29" t="n"/>
+      <c r="L26" s="36" t="n"/>
+      <c r="M26" s="16" t="n"/>
+      <c r="N26" s="37" t="n"/>
+      <c r="O26" s="38" t="n"/>
+      <c r="P26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>H675934</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>Ziani</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>Saad</t>
+        </is>
+      </c>
+      <c r="D27" s="35" t="n"/>
+      <c r="E27" s="29" t="n"/>
+      <c r="F27" s="29" t="n"/>
+      <c r="G27" s="29" t="n"/>
+      <c r="H27" s="29" t="n"/>
+      <c r="I27" s="29" t="n"/>
+      <c r="J27" s="29" t="n"/>
+      <c r="K27" s="29" t="n"/>
+      <c r="L27" s="36" t="n"/>
+      <c r="M27" s="16" t="n"/>
+      <c r="N27" s="37" t="n"/>
+      <c r="O27" s="38" t="n"/>
+      <c r="P27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="39" t="inlineStr">
+        <is>
+          <t>G116985</t>
+        </is>
+      </c>
+      <c r="B28" s="39" t="inlineStr">
+        <is>
+          <t>Azri</t>
+        </is>
+      </c>
+      <c r="C28" s="39" t="inlineStr">
+        <is>
+          <t>Basma</t>
+        </is>
+      </c>
+      <c r="D28" s="35" t="n"/>
+      <c r="E28" s="29" t="n"/>
+      <c r="F28" s="29" t="n"/>
+      <c r="G28" s="29" t="n"/>
+      <c r="H28" s="29" t="n"/>
+      <c r="I28" s="29" t="n"/>
+      <c r="J28" s="29" t="n"/>
+      <c r="K28" s="29" t="n"/>
+      <c r="L28" s="36" t="n"/>
+      <c r="M28" s="16" t="n"/>
+      <c r="N28" s="37" t="n"/>
+      <c r="O28" s="38" t="n"/>
+      <c r="P28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>M535134</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>Bouchta</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>Othmane</t>
+        </is>
+      </c>
+      <c r="D29" s="35" t="n"/>
+      <c r="E29" s="29" t="n"/>
+      <c r="F29" s="29" t="n"/>
+      <c r="G29" s="29" t="n"/>
+      <c r="H29" s="29" t="n"/>
+      <c r="I29" s="29" t="n"/>
+      <c r="J29" s="29" t="n"/>
+      <c r="K29" s="29" t="n"/>
+      <c r="L29" s="36" t="n"/>
+      <c r="M29" s="16" t="n"/>
+      <c r="N29" s="37" t="n"/>
+      <c r="O29" s="38" t="n"/>
+      <c r="P29" s="31" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="39" t="inlineStr">
+        <is>
+          <t>R487780</t>
+        </is>
+      </c>
+      <c r="B30" s="39" t="inlineStr">
+        <is>
+          <t>Chaibi</t>
+        </is>
+      </c>
+      <c r="C30" s="39" t="inlineStr">
+        <is>
+          <t>Sanae</t>
+        </is>
+      </c>
+      <c r="D30" s="35" t="n"/>
+      <c r="E30" s="29" t="n"/>
+      <c r="F30" s="29" t="n"/>
+      <c r="G30" s="29" t="n"/>
+      <c r="H30" s="29" t="n"/>
+      <c r="I30" s="29" t="n"/>
+      <c r="J30" s="29" t="n"/>
+      <c r="K30" s="29" t="n"/>
+      <c r="L30" s="36" t="n"/>
+      <c r="M30" s="16" t="n"/>
+      <c r="N30" s="37" t="n"/>
+      <c r="O30" s="38" t="n"/>
+      <c r="P30" s="31" t="n"/>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>F608380</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>Derfoufi</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>Khalid</t>
+        </is>
+      </c>
+      <c r="D31" s="35" t="n"/>
+      <c r="E31" s="29" t="n"/>
+      <c r="F31" s="29" t="n"/>
+      <c r="G31" s="29" t="n"/>
+      <c r="H31" s="29" t="n"/>
+      <c r="I31" s="29" t="n"/>
+      <c r="J31" s="29" t="n"/>
+      <c r="K31" s="29" t="n"/>
+      <c r="L31" s="36" t="n"/>
+      <c r="M31" s="16" t="n"/>
+      <c r="N31" s="37" t="n"/>
+      <c r="O31" s="38" t="n"/>
+      <c r="P31" s="31" t="n"/>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="39" t="inlineStr">
+        <is>
+          <t>N915546</t>
+        </is>
+      </c>
+      <c r="B32" s="39" t="inlineStr">
+        <is>
+          <t>Elouafi</t>
+        </is>
+      </c>
+      <c r="C32" s="39" t="inlineStr">
+        <is>
+          <t>Loubna</t>
+        </is>
+      </c>
+      <c r="D32" s="35" t="n"/>
+      <c r="E32" s="29" t="n"/>
+      <c r="F32" s="29" t="n"/>
+      <c r="G32" s="29" t="n"/>
+      <c r="H32" s="29" t="n"/>
+      <c r="I32" s="29" t="n"/>
+      <c r="J32" s="29" t="n"/>
+      <c r="K32" s="29" t="n"/>
+      <c r="L32" s="36" t="n"/>
+      <c r="M32" s="16" t="n"/>
+      <c r="N32" s="37" t="n"/>
+      <c r="O32" s="38" t="n"/>
+      <c r="P32" s="31" t="n"/>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>H718051</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>Fekhari</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>Anas</t>
+        </is>
+      </c>
+      <c r="D33" s="35" t="n"/>
+      <c r="E33" s="29" t="n"/>
+      <c r="F33" s="29" t="n"/>
+      <c r="G33" s="29" t="n"/>
+      <c r="H33" s="29" t="n"/>
+      <c r="I33" s="29" t="n"/>
+      <c r="J33" s="29" t="n"/>
+      <c r="K33" s="29" t="n"/>
+      <c r="L33" s="36" t="n"/>
+      <c r="M33" s="16" t="n"/>
+      <c r="N33" s="37" t="n"/>
+      <c r="O33" s="38" t="n"/>
+      <c r="P33" s="31" t="n"/>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="39" t="inlineStr">
+        <is>
+          <t>T572193</t>
+        </is>
+      </c>
+      <c r="B34" s="39" t="inlineStr">
+        <is>
+          <t>Guennouni</t>
+        </is>
+      </c>
+      <c r="C34" s="39" t="inlineStr">
+        <is>
+          <t>Zineb</t>
+        </is>
+      </c>
+      <c r="D34" s="35" t="n"/>
+      <c r="E34" s="29" t="n"/>
+      <c r="F34" s="29" t="n"/>
+      <c r="G34" s="29" t="n"/>
+      <c r="H34" s="29" t="n"/>
+      <c r="I34" s="29" t="n"/>
+      <c r="J34" s="29" t="n"/>
+      <c r="K34" s="29" t="n"/>
+      <c r="L34" s="36" t="n"/>
+      <c r="M34" s="16" t="n"/>
+      <c r="N34" s="37" t="n"/>
+      <c r="O34" s="38" t="n"/>
+      <c r="P34" s="31" t="n"/>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>G223327</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>Hajouji</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>Reda</t>
+        </is>
+      </c>
+      <c r="D35" s="35" t="n"/>
+      <c r="E35" s="29" t="n"/>
+      <c r="F35" s="29" t="n"/>
+      <c r="G35" s="29" t="n"/>
+      <c r="H35" s="29" t="n"/>
+      <c r="I35" s="29" t="n"/>
+      <c r="J35" s="29" t="n"/>
+      <c r="K35" s="29" t="n"/>
+      <c r="L35" s="36" t="n"/>
+      <c r="M35" s="16" t="n"/>
+      <c r="N35" s="37" t="n"/>
+      <c r="O35" s="38" t="n"/>
+      <c r="P35" s="31" t="n"/>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="39" t="inlineStr">
+        <is>
+          <t>N900081</t>
+        </is>
+      </c>
+      <c r="B36" s="39" t="inlineStr">
+        <is>
+          <t>Ikken</t>
+        </is>
+      </c>
+      <c r="C36" s="39" t="inlineStr">
+        <is>
+          <t>Meryem</t>
+        </is>
+      </c>
+      <c r="D36" s="35" t="n"/>
+      <c r="E36" s="29" t="n"/>
+      <c r="F36" s="29" t="n"/>
+      <c r="G36" s="29" t="n"/>
+      <c r="H36" s="29" t="n"/>
+      <c r="I36" s="29" t="n"/>
+      <c r="J36" s="29" t="n"/>
+      <c r="K36" s="29" t="n"/>
+      <c r="L36" s="36" t="n"/>
+      <c r="M36" s="16" t="n"/>
+      <c r="N36" s="37" t="n"/>
+      <c r="O36" s="38" t="n"/>
+      <c r="P36" s="31" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="D2:M2"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/raw/gee_genie_electrique.xlsx
+++ b/data/raw/gee_genie_electrique.xlsx
@@ -4083,7 +4083,7 @@
         <v>9.210000000000001</v>
       </c>
       <c r="Y39" s="11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Z39" s="21" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z39"/>
+  <dimension ref="A1:Z38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7321,7 +7321,6 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="N2:W2"/>
@@ -7367,6 +7366,21 @@
           <t>DÉPARTEMENT GEE GÉNIE ÉLECTRIQUE ET ÉLECTRONIQUE — TROISIÈME ANNÉE</t>
         </is>
       </c>
+      <c r="B1" s="22" t="n"/>
+      <c r="C1" s="22" t="n"/>
+      <c r="D1" s="22" t="n"/>
+      <c r="E1" s="22" t="n"/>
+      <c r="F1" s="22" t="n"/>
+      <c r="G1" s="22" t="n"/>
+      <c r="H1" s="22" t="n"/>
+      <c r="I1" s="22" t="n"/>
+      <c r="J1" s="22" t="n"/>
+      <c r="K1" s="22" t="n"/>
+      <c r="L1" s="22" t="n"/>
+      <c r="M1" s="22" t="n"/>
+      <c r="N1" s="22" t="n"/>
+      <c r="O1" s="22" t="n"/>
+      <c r="P1" s="23" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="25" t="inlineStr">
@@ -7374,11 +7388,22 @@
           <t>Informations Générales</t>
         </is>
       </c>
+      <c r="B2" s="22" t="n"/>
+      <c r="C2" s="23" t="n"/>
       <c r="D2" s="25" t="inlineStr">
         <is>
           <t>SEMESTRE 5</t>
         </is>
       </c>
+      <c r="E2" s="22" t="n"/>
+      <c r="F2" s="22" t="n"/>
+      <c r="G2" s="22" t="n"/>
+      <c r="H2" s="22" t="n"/>
+      <c r="I2" s="22" t="n"/>
+      <c r="J2" s="22" t="n"/>
+      <c r="K2" s="22" t="n"/>
+      <c r="L2" s="22" t="n"/>
+      <c r="M2" s="23" t="n"/>
       <c r="N2" s="25" t="inlineStr">
         <is>
           <t>SEMESTRE 6</t>
@@ -7389,6 +7414,8 @@
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="3" t="n"/>
+      <c r="B3" s="22" t="n"/>
+      <c r="C3" s="23" t="n"/>
       <c r="D3" s="4" t="n"/>
       <c r="E3" s="4" t="inlineStr">
         <is>
